--- a/bucket_2_connector_pm_features.xlsx
+++ b/bucket_2_connector_pm_features.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I675"/>
+  <dimension ref="A1:I677"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -3658,7 +3658,7 @@
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H75" t="inlineStr">
@@ -3701,7 +3701,7 @@
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H76" t="inlineStr">
@@ -3748,7 +3748,7 @@
       </c>
       <c r="G77" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H77" t="inlineStr">
@@ -3838,7 +3838,7 @@
       </c>
       <c r="G79" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H79" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
@@ -4010,7 +4010,7 @@
       </c>
       <c r="G83" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H83" t="inlineStr">
@@ -4096,7 +4096,7 @@
       </c>
       <c r="G85" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H85" t="inlineStr">
@@ -4186,7 +4186,7 @@
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
@@ -4272,7 +4272,7 @@
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
@@ -4315,7 +4315,7 @@
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
@@ -4358,7 +4358,7 @@
       </c>
       <c r="G91" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H91" t="inlineStr">
@@ -4444,7 +4444,7 @@
       </c>
       <c r="G93" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H93" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
@@ -4573,7 +4573,7 @@
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -4616,7 +4616,7 @@
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
@@ -4659,7 +4659,7 @@
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
@@ -4702,7 +4702,7 @@
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
@@ -4788,7 +4788,7 @@
       </c>
       <c r="G101" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H101" t="inlineStr">
@@ -4874,7 +4874,7 @@
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
@@ -13055,17 +13055,17 @@
     <row r="292">
       <c r="A292" t="inlineStr">
         <is>
-          <t>inespay</t>
+          <t>imerchantsolutions</t>
         </is>
       </c>
       <c r="B292" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C292" t="inlineStr">
         <is>
-          <t>Sepa</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D292" t="inlineStr">
@@ -13098,17 +13098,17 @@
     <row r="293">
       <c r="A293" t="inlineStr">
         <is>
-          <t>itaubank</t>
+          <t>imerchantsolutions</t>
         </is>
       </c>
       <c r="B293" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C293" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D293" t="inlineStr">
@@ -13128,7 +13128,7 @@
       </c>
       <c r="G293" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H293" t="inlineStr">
@@ -13141,17 +13141,17 @@
     <row r="294">
       <c r="A294" t="inlineStr">
         <is>
-          <t>jpmorgan</t>
+          <t>inespay</t>
         </is>
       </c>
       <c r="B294" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C294" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Sepa</t>
         </is>
       </c>
       <c r="D294" t="inlineStr">
@@ -13171,7 +13171,7 @@
       </c>
       <c r="G294" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H294" t="inlineStr">
@@ -13184,17 +13184,17 @@
     <row r="295">
       <c r="A295" t="inlineStr">
         <is>
-          <t>jpmorgan</t>
+          <t>itaubank</t>
         </is>
       </c>
       <c r="B295" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C295" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="D295" t="inlineStr">
@@ -13227,17 +13227,17 @@
     <row r="296">
       <c r="A296" t="inlineStr">
         <is>
-          <t>klarna</t>
+          <t>jpmorgan</t>
         </is>
       </c>
       <c r="B296" t="inlineStr">
         <is>
-          <t>PayLater</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C296" t="inlineStr">
         <is>
-          <t>Klarna</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D296" t="inlineStr">
@@ -13257,7 +13257,7 @@
       </c>
       <c r="G296" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H296" t="inlineStr">
@@ -13270,17 +13270,17 @@
     <row r="297">
       <c r="A297" t="inlineStr">
         <is>
-          <t>loonio</t>
+          <t>jpmorgan</t>
         </is>
       </c>
       <c r="B297" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C297" t="inlineStr">
         <is>
-          <t>Interac</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D297" t="inlineStr">
@@ -13305,29 +13305,25 @@
       </c>
       <c r="H297" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I297" t="inlineStr">
-        <is>
-          <t>2026-04-21 01:04:46</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I297" t="inlineStr"/>
     </row>
     <row r="298">
       <c r="A298" t="inlineStr">
         <is>
-          <t>mifinity</t>
+          <t>klarna</t>
         </is>
       </c>
       <c r="B298" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>PayLater</t>
         </is>
       </c>
       <c r="C298" t="inlineStr">
         <is>
-          <t>Mifinity</t>
+          <t>Klarna</t>
         </is>
       </c>
       <c r="D298" t="inlineStr">
@@ -13352,29 +13348,25 @@
       </c>
       <c r="H298" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I298" t="inlineStr">
-        <is>
-          <t>2026-04-20 09:34:50</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I298" t="inlineStr"/>
     </row>
     <row r="299">
       <c r="A299" t="inlineStr">
         <is>
-          <t>mollie</t>
+          <t>loonio</t>
         </is>
       </c>
       <c r="B299" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C299" t="inlineStr">
         <is>
-          <t>Sepa</t>
+          <t>Interac</t>
         </is>
       </c>
       <c r="D299" t="inlineStr">
@@ -13394,30 +13386,34 @@
       </c>
       <c r="G299" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H299" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I299" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I299" t="inlineStr">
+        <is>
+          <t>2026-04-21 01:04:46</t>
+        </is>
+      </c>
     </row>
     <row r="300">
       <c r="A300" t="inlineStr">
         <is>
-          <t>mollie</t>
+          <t>mifinity</t>
         </is>
       </c>
       <c r="B300" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C300" t="inlineStr">
         <is>
-          <t>BancontactCard</t>
+          <t>Mifinity</t>
         </is>
       </c>
       <c r="D300" t="inlineStr">
@@ -13437,15 +13433,19 @@
       </c>
       <c r="G300" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H300" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I300" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I300" t="inlineStr">
+        <is>
+          <t>2026-04-20 09:34:50</t>
+        </is>
+      </c>
     </row>
     <row r="301">
       <c r="A301" t="inlineStr">
@@ -13455,12 +13455,12 @@
       </c>
       <c r="B301" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C301" t="inlineStr">
         <is>
-          <t>Eps</t>
+          <t>Sepa</t>
         </is>
       </c>
       <c r="D301" t="inlineStr">
@@ -13480,7 +13480,7 @@
       </c>
       <c r="G301" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H301" t="inlineStr">
@@ -13503,7 +13503,7 @@
       </c>
       <c r="C302" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>BancontactCard</t>
         </is>
       </c>
       <c r="D302" t="inlineStr">
@@ -13546,7 +13546,7 @@
       </c>
       <c r="C303" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Eps</t>
         </is>
       </c>
       <c r="D303" t="inlineStr">
@@ -13589,7 +13589,7 @@
       </c>
       <c r="C304" t="inlineStr">
         <is>
-          <t>Przelewy24</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D304" t="inlineStr">
@@ -13632,7 +13632,7 @@
       </c>
       <c r="C305" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D305" t="inlineStr">
@@ -13670,12 +13670,12 @@
       </c>
       <c r="B306" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C306" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Przelewy24</t>
         </is>
       </c>
       <c r="D306" t="inlineStr">
@@ -13700,14 +13700,10 @@
       </c>
       <c r="H306" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I306" t="inlineStr">
-        <is>
-          <t>2026-03-04 08:31:59</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I306" t="inlineStr"/>
     </row>
     <row r="307">
       <c r="A307" t="inlineStr">
@@ -13717,27 +13713,27 @@
       </c>
       <c r="B307" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C307" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D307" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E307" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F307" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G307" t="inlineStr">
@@ -13765,7 +13761,7 @@
       </c>
       <c r="C308" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D308" t="inlineStr">
@@ -13795,7 +13791,7 @@
       </c>
       <c r="I308" t="inlineStr">
         <is>
-          <t>2026-03-04 09:04:29</t>
+          <t>2026-03-04 08:31:59</t>
         </is>
       </c>
     </row>
@@ -13812,7 +13808,7 @@
       </c>
       <c r="C309" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D309" t="inlineStr">
@@ -13850,12 +13846,12 @@
       </c>
       <c r="B310" t="inlineStr">
         <is>
-          <t>PayLater</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C310" t="inlineStr">
         <is>
-          <t>Klarna</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D310" t="inlineStr">
@@ -13875,15 +13871,19 @@
       </c>
       <c r="G310" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H310" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I310" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I310" t="inlineStr">
+        <is>
+          <t>2026-03-04 09:04:29</t>
+        </is>
+      </c>
     </row>
     <row r="311">
       <c r="A311" t="inlineStr">
@@ -13893,32 +13893,32 @@
       </c>
       <c r="B311" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C311" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D311" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E311" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F311" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G311" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H311" t="inlineStr">
@@ -13936,12 +13936,12 @@
       </c>
       <c r="B312" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>PayLater</t>
         </is>
       </c>
       <c r="C312" t="inlineStr">
         <is>
-          <t>Paypal</t>
+          <t>Klarna</t>
         </is>
       </c>
       <c r="D312" t="inlineStr">
@@ -13974,17 +13974,17 @@
     <row r="313">
       <c r="A313" t="inlineStr">
         <is>
-          <t>moneris</t>
+          <t>mollie</t>
         </is>
       </c>
       <c r="B313" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C313" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D313" t="inlineStr">
@@ -14004,7 +14004,7 @@
       </c>
       <c r="G313" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H313" t="inlineStr">
@@ -14017,37 +14017,37 @@
     <row r="314">
       <c r="A314" t="inlineStr">
         <is>
-          <t>moneris</t>
+          <t>mollie</t>
         </is>
       </c>
       <c r="B314" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C314" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Paypal</t>
         </is>
       </c>
       <c r="D314" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E314" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F314" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G314" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H314" t="inlineStr">
@@ -14070,7 +14070,7 @@
       </c>
       <c r="C315" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D315" t="inlineStr">
@@ -14113,7 +14113,7 @@
       </c>
       <c r="C316" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D316" t="inlineStr">
@@ -14146,17 +14146,17 @@
     <row r="317">
       <c r="A317" t="inlineStr">
         <is>
-          <t>multisafepay</t>
+          <t>moneris</t>
         </is>
       </c>
       <c r="B317" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C317" t="inlineStr">
         <is>
-          <t>Eps</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D317" t="inlineStr">
@@ -14189,32 +14189,32 @@
     <row r="318">
       <c r="A318" t="inlineStr">
         <is>
-          <t>multisafepay</t>
+          <t>moneris</t>
         </is>
       </c>
       <c r="B318" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C318" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D318" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E318" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F318" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G318" t="inlineStr">
@@ -14242,7 +14242,7 @@
       </c>
       <c r="C319" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Eps</t>
         </is>
       </c>
       <c r="D319" t="inlineStr">
@@ -14285,7 +14285,7 @@
       </c>
       <c r="C320" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D320" t="inlineStr">
@@ -14328,7 +14328,7 @@
       </c>
       <c r="C321" t="inlineStr">
         <is>
-          <t>Trustly</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D321" t="inlineStr">
@@ -14366,12 +14366,12 @@
       </c>
       <c r="B322" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C322" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D322" t="inlineStr">
@@ -14409,27 +14409,27 @@
       </c>
       <c r="B323" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C323" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Trustly</t>
         </is>
       </c>
       <c r="D323" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E323" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F323" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G323" t="inlineStr">
@@ -14457,7 +14457,7 @@
       </c>
       <c r="C324" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D324" t="inlineStr">
@@ -14500,7 +14500,7 @@
       </c>
       <c r="C325" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D325" t="inlineStr">
@@ -14538,12 +14538,12 @@
       </c>
       <c r="B326" t="inlineStr">
         <is>
-          <t>PayLater</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C326" t="inlineStr">
         <is>
-          <t>Klarna</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D326" t="inlineStr">
@@ -14563,7 +14563,7 @@
       </c>
       <c r="G326" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H326" t="inlineStr">
@@ -14581,32 +14581,32 @@
       </c>
       <c r="B327" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C327" t="inlineStr">
         <is>
-          <t>AliPay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D327" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E327" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F327" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G327" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H327" t="inlineStr">
@@ -14624,12 +14624,12 @@
       </c>
       <c r="B328" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>PayLater</t>
         </is>
       </c>
       <c r="C328" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Klarna</t>
         </is>
       </c>
       <c r="D328" t="inlineStr">
@@ -14672,22 +14672,22 @@
       </c>
       <c r="C329" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>AliPay</t>
         </is>
       </c>
       <c r="D329" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E329" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F329" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G329" t="inlineStr">
@@ -14715,7 +14715,7 @@
       </c>
       <c r="C330" t="inlineStr">
         <is>
-          <t>MbWay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D330" t="inlineStr">
@@ -14758,22 +14758,22 @@
       </c>
       <c r="C331" t="inlineStr">
         <is>
-          <t>Paypal</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D331" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E331" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F331" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G331" t="inlineStr">
@@ -14801,7 +14801,7 @@
       </c>
       <c r="C332" t="inlineStr">
         <is>
-          <t>WeChatPay</t>
+          <t>MbWay</t>
         </is>
       </c>
       <c r="D332" t="inlineStr">
@@ -14834,17 +14834,17 @@
     <row r="333">
       <c r="A333" t="inlineStr">
         <is>
-          <t>nexinets</t>
+          <t>multisafepay</t>
         </is>
       </c>
       <c r="B333" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C333" t="inlineStr">
         <is>
-          <t>Eps</t>
+          <t>Paypal</t>
         </is>
       </c>
       <c r="D333" t="inlineStr">
@@ -14864,7 +14864,7 @@
       </c>
       <c r="G333" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H333" t="inlineStr">
@@ -14877,17 +14877,17 @@
     <row r="334">
       <c r="A334" t="inlineStr">
         <is>
-          <t>nexinets</t>
+          <t>multisafepay</t>
         </is>
       </c>
       <c r="B334" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C334" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>WeChatPay</t>
         </is>
       </c>
       <c r="D334" t="inlineStr">
@@ -14907,7 +14907,7 @@
       </c>
       <c r="G334" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H334" t="inlineStr">
@@ -14930,7 +14930,7 @@
       </c>
       <c r="C335" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Eps</t>
         </is>
       </c>
       <c r="D335" t="inlineStr">
@@ -14973,7 +14973,7 @@
       </c>
       <c r="C336" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D336" t="inlineStr">
@@ -15011,12 +15011,12 @@
       </c>
       <c r="B337" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C337" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D337" t="inlineStr">
@@ -15054,27 +15054,27 @@
       </c>
       <c r="B338" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C338" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D338" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E338" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F338" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G338" t="inlineStr">
@@ -15102,7 +15102,7 @@
       </c>
       <c r="C339" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D339" t="inlineStr">
@@ -15145,7 +15145,7 @@
       </c>
       <c r="C340" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D340" t="inlineStr">
@@ -15183,12 +15183,12 @@
       </c>
       <c r="B341" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C341" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D341" t="inlineStr">
@@ -15208,7 +15208,7 @@
       </c>
       <c r="G341" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H341" t="inlineStr">
@@ -15226,32 +15226,32 @@
       </c>
       <c r="B342" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C342" t="inlineStr">
         <is>
-          <t>Paypal</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D342" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E342" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F342" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G342" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H342" t="inlineStr">
@@ -15264,17 +15264,17 @@
     <row r="343">
       <c r="A343" t="inlineStr">
         <is>
-          <t>nexixpay</t>
+          <t>nexinets</t>
         </is>
       </c>
       <c r="B343" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C343" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D343" t="inlineStr">
@@ -15294,54 +15294,50 @@
       </c>
       <c r="G343" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H343" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I343" t="inlineStr">
-        <is>
-          <t>2026-04-20 21:31:13</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I343" t="inlineStr"/>
     </row>
     <row r="344">
       <c r="A344" t="inlineStr">
         <is>
-          <t>nexixpay</t>
+          <t>nexinets</t>
         </is>
       </c>
       <c r="B344" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C344" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Paypal</t>
         </is>
       </c>
       <c r="D344" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E344" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F344" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G344" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H344" t="inlineStr">
@@ -15364,7 +15360,7 @@
       </c>
       <c r="C345" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D345" t="inlineStr">
@@ -15394,7 +15390,7 @@
       </c>
       <c r="I345" t="inlineStr">
         <is>
-          <t>2026-04-20 21:30:56</t>
+          <t>2026-04-20 21:31:13</t>
         </is>
       </c>
     </row>
@@ -15411,7 +15407,7 @@
       </c>
       <c r="C346" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D346" t="inlineStr">
@@ -15444,7 +15440,7 @@
     <row r="347">
       <c r="A347" t="inlineStr">
         <is>
-          <t>nmi</t>
+          <t>nexixpay</t>
         </is>
       </c>
       <c r="B347" t="inlineStr">
@@ -15454,7 +15450,7 @@
       </c>
       <c r="C347" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D347" t="inlineStr">
@@ -15484,14 +15480,14 @@
       </c>
       <c r="I347" t="inlineStr">
         <is>
-          <t>2026-04-21 00:34:17</t>
+          <t>2026-04-20 21:30:56</t>
         </is>
       </c>
     </row>
     <row r="348">
       <c r="A348" t="inlineStr">
         <is>
-          <t>nmi</t>
+          <t>nexixpay</t>
         </is>
       </c>
       <c r="B348" t="inlineStr">
@@ -15501,7 +15497,7 @@
       </c>
       <c r="C348" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D348" t="inlineStr">
@@ -15544,7 +15540,7 @@
       </c>
       <c r="C349" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D349" t="inlineStr">
@@ -15574,7 +15570,7 @@
       </c>
       <c r="I349" t="inlineStr">
         <is>
-          <t>2026-04-20 18:03:51</t>
+          <t>2026-04-21 00:34:17</t>
         </is>
       </c>
     </row>
@@ -15591,7 +15587,7 @@
       </c>
       <c r="C350" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D350" t="inlineStr">
@@ -15629,12 +15625,12 @@
       </c>
       <c r="B351" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C351" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D351" t="inlineStr">
@@ -15654,7 +15650,7 @@
       </c>
       <c r="G351" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H351" t="inlineStr">
@@ -15664,7 +15660,7 @@
       </c>
       <c r="I351" t="inlineStr">
         <is>
-          <t>2026-04-20 22:04:34</t>
+          <t>2026-04-20 18:03:51</t>
         </is>
       </c>
     </row>
@@ -15676,12 +15672,12 @@
       </c>
       <c r="B352" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C352" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D352" t="inlineStr">
@@ -15701,7 +15697,7 @@
       </c>
       <c r="G352" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H352" t="inlineStr">
@@ -15724,7 +15720,7 @@
       </c>
       <c r="C353" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D353" t="inlineStr">
@@ -15754,7 +15750,7 @@
       </c>
       <c r="I353" t="inlineStr">
         <is>
-          <t>2026-03-31 22:08:04</t>
+          <t>2026-04-20 22:04:34</t>
         </is>
       </c>
     </row>
@@ -15771,7 +15767,7 @@
       </c>
       <c r="C354" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D354" t="inlineStr">
@@ -15804,17 +15800,17 @@
     <row r="355">
       <c r="A355" t="inlineStr">
         <is>
-          <t>noon</t>
+          <t>nmi</t>
         </is>
       </c>
       <c r="B355" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C355" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D355" t="inlineStr">
@@ -15834,7 +15830,7 @@
       </c>
       <c r="G355" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H355" t="inlineStr">
@@ -15844,24 +15840,24 @@
       </c>
       <c r="I355" t="inlineStr">
         <is>
-          <t>2026-04-20 23:42:38</t>
+          <t>2026-03-31 22:08:04</t>
         </is>
       </c>
     </row>
     <row r="356">
       <c r="A356" t="inlineStr">
         <is>
-          <t>noon</t>
+          <t>nmi</t>
         </is>
       </c>
       <c r="B356" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C356" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D356" t="inlineStr">
@@ -15881,19 +15877,15 @@
       </c>
       <c r="G356" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H356" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I356" t="inlineStr">
-        <is>
-          <t>2026-04-20 23:42:38</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I356" t="inlineStr"/>
     </row>
     <row r="357">
       <c r="A357" t="inlineStr">
@@ -15908,7 +15900,7 @@
       </c>
       <c r="C357" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D357" t="inlineStr">
@@ -15938,7 +15930,7 @@
       </c>
       <c r="I357" t="inlineStr">
         <is>
-          <t>2026-04-21 00:50:44</t>
+          <t>2026-04-20 23:42:38</t>
         </is>
       </c>
     </row>
@@ -15955,7 +15947,7 @@
       </c>
       <c r="C358" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D358" t="inlineStr">
@@ -15985,7 +15977,7 @@
       </c>
       <c r="I358" t="inlineStr">
         <is>
-          <t>2026-04-21 00:50:44</t>
+          <t>2026-04-20 23:42:38</t>
         </is>
       </c>
     </row>
@@ -15997,12 +15989,12 @@
       </c>
       <c r="B359" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C359" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D359" t="inlineStr">
@@ -16022,7 +16014,7 @@
       </c>
       <c r="G359" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H359" t="inlineStr">
@@ -16032,7 +16024,7 @@
       </c>
       <c r="I359" t="inlineStr">
         <is>
-          <t>2026-04-21 01:19:40</t>
+          <t>2026-04-21 00:50:44</t>
         </is>
       </c>
     </row>
@@ -16044,12 +16036,12 @@
       </c>
       <c r="B360" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C360" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D360" t="inlineStr">
@@ -16069,7 +16061,7 @@
       </c>
       <c r="G360" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H360" t="inlineStr">
@@ -16079,7 +16071,7 @@
       </c>
       <c r="I360" t="inlineStr">
         <is>
-          <t>2026-04-20 22:44:47</t>
+          <t>2026-04-21 00:50:44</t>
         </is>
       </c>
     </row>
@@ -16096,7 +16088,7 @@
       </c>
       <c r="C361" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D361" t="inlineStr">
@@ -16121,10 +16113,14 @@
       </c>
       <c r="H361" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I361" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I361" t="inlineStr">
+        <is>
+          <t>2026-04-21 01:19:40</t>
+        </is>
+      </c>
     </row>
     <row r="362">
       <c r="A362" t="inlineStr">
@@ -16139,7 +16135,7 @@
       </c>
       <c r="C362" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D362" t="inlineStr">
@@ -16164,10 +16160,14 @@
       </c>
       <c r="H362" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I362" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I362" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:44:47</t>
+        </is>
+      </c>
     </row>
     <row r="363">
       <c r="A363" t="inlineStr">
@@ -16182,7 +16182,7 @@
       </c>
       <c r="C363" t="inlineStr">
         <is>
-          <t>Paypal</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D363" t="inlineStr">
@@ -16215,32 +16215,32 @@
     <row r="364">
       <c r="A364" t="inlineStr">
         <is>
-          <t>novalnet</t>
+          <t>noon</t>
         </is>
       </c>
       <c r="B364" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C364" t="inlineStr">
         <is>
-          <t>Sepa</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D364" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E364" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F364" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G364" t="inlineStr">
@@ -16250,44 +16250,40 @@
       </c>
       <c r="H364" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I364" t="inlineStr">
-        <is>
-          <t>2026-04-20 19:37:58</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I364" t="inlineStr"/>
     </row>
     <row r="365">
       <c r="A365" t="inlineStr">
         <is>
-          <t>novalnet</t>
+          <t>noon</t>
         </is>
       </c>
       <c r="B365" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C365" t="inlineStr">
         <is>
-          <t>Sepa</t>
+          <t>Paypal</t>
         </is>
       </c>
       <c r="D365" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E365" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F365" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G365" t="inlineStr">
@@ -16315,7 +16311,7 @@
       </c>
       <c r="C366" t="inlineStr">
         <is>
-          <t>SepaGuarenteedDebit</t>
+          <t>Sepa</t>
         </is>
       </c>
       <c r="D366" t="inlineStr">
@@ -16335,15 +16331,19 @@
       </c>
       <c r="G366" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H366" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I366" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I366" t="inlineStr">
+        <is>
+          <t>2026-04-20 19:37:58</t>
+        </is>
+      </c>
     </row>
     <row r="367">
       <c r="A367" t="inlineStr">
@@ -16358,7 +16358,7 @@
       </c>
       <c r="C367" t="inlineStr">
         <is>
-          <t>SepaGuarenteedDebit</t>
+          <t>Sepa</t>
         </is>
       </c>
       <c r="D367" t="inlineStr">
@@ -16396,12 +16396,12 @@
       </c>
       <c r="B368" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C368" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>SepaGuarenteedDebit</t>
         </is>
       </c>
       <c r="D368" t="inlineStr">
@@ -16426,14 +16426,10 @@
       </c>
       <c r="H368" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I368" t="inlineStr">
-        <is>
-          <t>2026-04-21 00:01:54</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I368" t="inlineStr"/>
     </row>
     <row r="369">
       <c r="A369" t="inlineStr">
@@ -16443,12 +16439,12 @@
       </c>
       <c r="B369" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C369" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>SepaGuarenteedDebit</t>
         </is>
       </c>
       <c r="D369" t="inlineStr">
@@ -16468,7 +16464,7 @@
       </c>
       <c r="G369" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H369" t="inlineStr">
@@ -16491,7 +16487,7 @@
       </c>
       <c r="C370" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D370" t="inlineStr">
@@ -16521,7 +16517,7 @@
       </c>
       <c r="I370" t="inlineStr">
         <is>
-          <t>2026-04-21 01:06:07</t>
+          <t>2026-04-21 00:01:54</t>
         </is>
       </c>
     </row>
@@ -16538,7 +16534,7 @@
       </c>
       <c r="C371" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D371" t="inlineStr">
@@ -16576,12 +16572,12 @@
       </c>
       <c r="B372" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C372" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D372" t="inlineStr">
@@ -16601,7 +16597,7 @@
       </c>
       <c r="G372" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H372" t="inlineStr">
@@ -16611,7 +16607,7 @@
       </c>
       <c r="I372" t="inlineStr">
         <is>
-          <t>2026-04-21 00:01:56</t>
+          <t>2026-04-21 01:06:07</t>
         </is>
       </c>
     </row>
@@ -16623,12 +16619,12 @@
       </c>
       <c r="B373" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C373" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D373" t="inlineStr">
@@ -16648,7 +16644,7 @@
       </c>
       <c r="G373" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H373" t="inlineStr">
@@ -16671,7 +16667,7 @@
       </c>
       <c r="C374" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D374" t="inlineStr">
@@ -16701,7 +16697,7 @@
       </c>
       <c r="I374" t="inlineStr">
         <is>
-          <t>2026-04-20 00:00:28</t>
+          <t>2026-04-21 00:01:56</t>
         </is>
       </c>
     </row>
@@ -16718,7 +16714,7 @@
       </c>
       <c r="C375" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D375" t="inlineStr">
@@ -16761,7 +16757,7 @@
       </c>
       <c r="C376" t="inlineStr">
         <is>
-          <t>Paypal</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D376" t="inlineStr">
@@ -16791,7 +16787,7 @@
       </c>
       <c r="I376" t="inlineStr">
         <is>
-          <t>2026-04-21 01:16:53</t>
+          <t>2026-04-20 00:00:28</t>
         </is>
       </c>
     </row>
@@ -16808,7 +16804,7 @@
       </c>
       <c r="C377" t="inlineStr">
         <is>
-          <t>Paypal</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D377" t="inlineStr">
@@ -16841,17 +16837,17 @@
     <row r="378">
       <c r="A378" t="inlineStr">
         <is>
-          <t>nuvei</t>
+          <t>novalnet</t>
         </is>
       </c>
       <c r="B378" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C378" t="inlineStr">
         <is>
-          <t>Eps</t>
+          <t>Paypal</t>
         </is>
       </c>
       <c r="D378" t="inlineStr">
@@ -16871,50 +16867,54 @@
       </c>
       <c r="G378" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H378" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I378" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I378" t="inlineStr">
+        <is>
+          <t>2026-04-21 01:16:53</t>
+        </is>
+      </c>
     </row>
     <row r="379">
       <c r="A379" t="inlineStr">
         <is>
-          <t>nuvei</t>
+          <t>novalnet</t>
         </is>
       </c>
       <c r="B379" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C379" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>Paypal</t>
         </is>
       </c>
       <c r="D379" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E379" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F379" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G379" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H379" t="inlineStr">
@@ -16937,7 +16937,7 @@
       </c>
       <c r="C380" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Eps</t>
         </is>
       </c>
       <c r="D380" t="inlineStr">
@@ -16980,7 +16980,7 @@
       </c>
       <c r="C381" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D381" t="inlineStr">
@@ -17018,12 +17018,12 @@
       </c>
       <c r="B382" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C382" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D382" t="inlineStr">
@@ -17048,14 +17048,10 @@
       </c>
       <c r="H382" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I382" t="inlineStr">
-        <is>
-          <t>2026-04-20 16:00:22</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I382" t="inlineStr"/>
     </row>
     <row r="383">
       <c r="A383" t="inlineStr">
@@ -17065,27 +17061,27 @@
       </c>
       <c r="B383" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C383" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D383" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E383" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F383" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G383" t="inlineStr">
@@ -17113,7 +17109,7 @@
       </c>
       <c r="C384" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D384" t="inlineStr">
@@ -17143,7 +17139,7 @@
       </c>
       <c r="I384" t="inlineStr">
         <is>
-          <t>2026-04-21 00:10:29</t>
+          <t>2026-04-20 16:00:22</t>
         </is>
       </c>
     </row>
@@ -17160,7 +17156,7 @@
       </c>
       <c r="C385" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D385" t="inlineStr">
@@ -17198,12 +17194,12 @@
       </c>
       <c r="B386" t="inlineStr">
         <is>
-          <t>NetworkToken</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C386" t="inlineStr">
         <is>
-          <t>NetworkToken</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D386" t="inlineStr">
@@ -17228,10 +17224,14 @@
       </c>
       <c r="H386" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I386" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I386" t="inlineStr">
+        <is>
+          <t>2026-04-21 00:10:29</t>
+        </is>
+      </c>
     </row>
     <row r="387">
       <c r="A387" t="inlineStr">
@@ -17241,32 +17241,32 @@
       </c>
       <c r="B387" t="inlineStr">
         <is>
-          <t>PayLater</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C387" t="inlineStr">
         <is>
-          <t>AfterpayClearpay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D387" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E387" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F387" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G387" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H387" t="inlineStr">
@@ -17284,12 +17284,12 @@
       </c>
       <c r="B388" t="inlineStr">
         <is>
-          <t>PayLater</t>
+          <t>NetworkToken</t>
         </is>
       </c>
       <c r="C388" t="inlineStr">
         <is>
-          <t>Klarna</t>
+          <t>NetworkToken</t>
         </is>
       </c>
       <c r="D388" t="inlineStr">
@@ -17309,7 +17309,7 @@
       </c>
       <c r="G388" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H388" t="inlineStr">
@@ -17327,12 +17327,12 @@
       </c>
       <c r="B389" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>PayLater</t>
         </is>
       </c>
       <c r="C389" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>AfterpayClearpay</t>
         </is>
       </c>
       <c r="D389" t="inlineStr">
@@ -17370,27 +17370,27 @@
       </c>
       <c r="B390" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>PayLater</t>
         </is>
       </c>
       <c r="C390" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Klarna</t>
         </is>
       </c>
       <c r="D390" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E390" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F390" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G390" t="inlineStr">
@@ -17418,7 +17418,7 @@
       </c>
       <c r="C391" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D391" t="inlineStr">
@@ -17461,7 +17461,7 @@
       </c>
       <c r="C392" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D392" t="inlineStr">
@@ -17504,7 +17504,7 @@
       </c>
       <c r="C393" t="inlineStr">
         <is>
-          <t>Paypal</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D393" t="inlineStr">
@@ -17537,37 +17537,37 @@
     <row r="394">
       <c r="A394" t="inlineStr">
         <is>
-          <t>opennode</t>
+          <t>nuvei</t>
         </is>
       </c>
       <c r="B394" t="inlineStr">
         <is>
-          <t>Crypto</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C394" t="inlineStr">
         <is>
-          <t>CryptoCurrency</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D394" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E394" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F394" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G394" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H394" t="inlineStr">
@@ -17580,17 +17580,17 @@
     <row r="395">
       <c r="A395" t="inlineStr">
         <is>
-          <t>paybox</t>
+          <t>nuvei</t>
         </is>
       </c>
       <c r="B395" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C395" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Paypal</t>
         </is>
       </c>
       <c r="D395" t="inlineStr">
@@ -17610,7 +17610,7 @@
       </c>
       <c r="G395" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H395" t="inlineStr">
@@ -17623,37 +17623,37 @@
     <row r="396">
       <c r="A396" t="inlineStr">
         <is>
-          <t>paybox</t>
+          <t>opennode</t>
         </is>
       </c>
       <c r="B396" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Crypto</t>
         </is>
       </c>
       <c r="C396" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>CryptoCurrency</t>
         </is>
       </c>
       <c r="D396" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E396" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F396" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G396" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H396" t="inlineStr">
@@ -17676,7 +17676,7 @@
       </c>
       <c r="C397" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D397" t="inlineStr">
@@ -17719,7 +17719,7 @@
       </c>
       <c r="C398" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D398" t="inlineStr">
@@ -17752,7 +17752,7 @@
     <row r="399">
       <c r="A399" t="inlineStr">
         <is>
-          <t>payeezy</t>
+          <t>paybox</t>
         </is>
       </c>
       <c r="B399" t="inlineStr">
@@ -17762,7 +17762,7 @@
       </c>
       <c r="C399" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D399" t="inlineStr">
@@ -17782,7 +17782,7 @@
       </c>
       <c r="G399" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H399" t="inlineStr">
@@ -17795,7 +17795,7 @@
     <row r="400">
       <c r="A400" t="inlineStr">
         <is>
-          <t>payeezy</t>
+          <t>paybox</t>
         </is>
       </c>
       <c r="B400" t="inlineStr">
@@ -17805,7 +17805,7 @@
       </c>
       <c r="C400" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D400" t="inlineStr">
@@ -17825,7 +17825,7 @@
       </c>
       <c r="G400" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H400" t="inlineStr">
@@ -17838,17 +17838,17 @@
     <row r="401">
       <c r="A401" t="inlineStr">
         <is>
-          <t>payjustnow</t>
+          <t>payeezy</t>
         </is>
       </c>
       <c r="B401" t="inlineStr">
         <is>
-          <t>PayLater</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C401" t="inlineStr">
         <is>
-          <t>Payjustnow</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D401" t="inlineStr">
@@ -17881,32 +17881,32 @@
     <row r="402">
       <c r="A402" t="inlineStr">
         <is>
-          <t>payjustnowinstore</t>
+          <t>payeezy</t>
         </is>
       </c>
       <c r="B402" t="inlineStr">
         <is>
-          <t>PayLater</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C402" t="inlineStr">
         <is>
-          <t>Payjustnow</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D402" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E402" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F402" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G402" t="inlineStr">
@@ -17924,17 +17924,17 @@
     <row r="403">
       <c r="A403" t="inlineStr">
         <is>
-          <t>payload</t>
+          <t>payjustnow</t>
         </is>
       </c>
       <c r="B403" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>PayLater</t>
         </is>
       </c>
       <c r="C403" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>Payjustnow</t>
         </is>
       </c>
       <c r="D403" t="inlineStr">
@@ -17954,54 +17954,50 @@
       </c>
       <c r="G403" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H403" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I403" t="inlineStr">
-        <is>
-          <t>2026-04-21 00:41:56</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I403" t="inlineStr"/>
     </row>
     <row r="404">
       <c r="A404" t="inlineStr">
         <is>
-          <t>payload</t>
+          <t>payjustnowinstore</t>
         </is>
       </c>
       <c r="B404" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>PayLater</t>
         </is>
       </c>
       <c r="C404" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>Payjustnow</t>
         </is>
       </c>
       <c r="D404" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E404" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F404" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G404" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H404" t="inlineStr">
@@ -18019,12 +18015,12 @@
       </c>
       <c r="B405" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C405" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D405" t="inlineStr">
@@ -18044,7 +18040,7 @@
       </c>
       <c r="G405" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H405" t="inlineStr">
@@ -18054,7 +18050,7 @@
       </c>
       <c r="I405" t="inlineStr">
         <is>
-          <t>2026-04-16 16:03:21</t>
+          <t>2026-04-21 00:41:56</t>
         </is>
       </c>
     </row>
@@ -18066,12 +18062,12 @@
       </c>
       <c r="B406" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C406" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D406" t="inlineStr">
@@ -18091,7 +18087,7 @@
       </c>
       <c r="G406" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H406" t="inlineStr">
@@ -18114,7 +18110,7 @@
       </c>
       <c r="C407" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D407" t="inlineStr">
@@ -18144,7 +18140,7 @@
       </c>
       <c r="I407" t="inlineStr">
         <is>
-          <t>2026-04-20 14:18:05</t>
+          <t>2026-04-16 16:03:21</t>
         </is>
       </c>
     </row>
@@ -18161,7 +18157,7 @@
       </c>
       <c r="C408" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D408" t="inlineStr">
@@ -18194,7 +18190,7 @@
     <row r="409">
       <c r="A409" t="inlineStr">
         <is>
-          <t>payme</t>
+          <t>payload</t>
         </is>
       </c>
       <c r="B409" t="inlineStr">
@@ -18204,7 +18200,7 @@
       </c>
       <c r="C409" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D409" t="inlineStr">
@@ -18224,20 +18220,24 @@
       </c>
       <c r="G409" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H409" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I409" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I409" t="inlineStr">
+        <is>
+          <t>2026-04-20 14:18:05</t>
+        </is>
+      </c>
     </row>
     <row r="410">
       <c r="A410" t="inlineStr">
         <is>
-          <t>payme</t>
+          <t>payload</t>
         </is>
       </c>
       <c r="B410" t="inlineStr">
@@ -18247,7 +18247,7 @@
       </c>
       <c r="C410" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D410" t="inlineStr">
@@ -18267,7 +18267,7 @@
       </c>
       <c r="G410" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H410" t="inlineStr">
@@ -18290,7 +18290,7 @@
       </c>
       <c r="C411" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D411" t="inlineStr">
@@ -18333,7 +18333,7 @@
       </c>
       <c r="C412" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D412" t="inlineStr">
@@ -18371,12 +18371,12 @@
       </c>
       <c r="B413" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C413" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D413" t="inlineStr">
@@ -18414,12 +18414,12 @@
       </c>
       <c r="B414" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C414" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D414" t="inlineStr">
@@ -18452,17 +18452,17 @@
     <row r="415">
       <c r="A415" t="inlineStr">
         <is>
-          <t>paypal</t>
+          <t>payme</t>
         </is>
       </c>
       <c r="B415" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C415" t="inlineStr">
         <is>
-          <t>Eps</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D415" t="inlineStr">
@@ -18482,7 +18482,7 @@
       </c>
       <c r="G415" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H415" t="inlineStr">
@@ -18495,37 +18495,37 @@
     <row r="416">
       <c r="A416" t="inlineStr">
         <is>
-          <t>paypal</t>
+          <t>payme</t>
         </is>
       </c>
       <c r="B416" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C416" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D416" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E416" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F416" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G416" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H416" t="inlineStr">
@@ -18548,7 +18548,7 @@
       </c>
       <c r="C417" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Eps</t>
         </is>
       </c>
       <c r="D417" t="inlineStr">
@@ -18591,7 +18591,7 @@
       </c>
       <c r="C418" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D418" t="inlineStr">
@@ -18629,12 +18629,12 @@
       </c>
       <c r="B419" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C419" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D419" t="inlineStr">
@@ -18659,14 +18659,10 @@
       </c>
       <c r="H419" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I419" t="inlineStr">
-        <is>
-          <t>2026-04-21 01:32:54</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I419" t="inlineStr"/>
     </row>
     <row r="420">
       <c r="A420" t="inlineStr">
@@ -18676,27 +18672,27 @@
       </c>
       <c r="B420" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C420" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D420" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E420" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F420" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G420" t="inlineStr">
@@ -18724,7 +18720,7 @@
       </c>
       <c r="C421" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D421" t="inlineStr">
@@ -18754,7 +18750,7 @@
       </c>
       <c r="I421" t="inlineStr">
         <is>
-          <t>2026-04-21 01:38:06</t>
+          <t>2026-04-21 01:32:54</t>
         </is>
       </c>
     </row>
@@ -18771,7 +18767,7 @@
       </c>
       <c r="C422" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D422" t="inlineStr">
@@ -18809,12 +18805,12 @@
       </c>
       <c r="B423" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C423" t="inlineStr">
         <is>
-          <t>Paypal</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D423" t="inlineStr">
@@ -18834,7 +18830,7 @@
       </c>
       <c r="G423" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H423" t="inlineStr">
@@ -18844,7 +18840,7 @@
       </c>
       <c r="I423" t="inlineStr">
         <is>
-          <t>2026-04-20 05:34:06</t>
+          <t>2026-04-21 01:38:06</t>
         </is>
       </c>
     </row>
@@ -18856,12 +18852,12 @@
       </c>
       <c r="B424" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C424" t="inlineStr">
         <is>
-          <t>Paypal</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D424" t="inlineStr">
@@ -18881,34 +18877,30 @@
       </c>
       <c r="G424" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H424" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I424" t="inlineStr">
-        <is>
-          <t>2026-04-14 16:59:43</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I424" t="inlineStr"/>
     </row>
     <row r="425">
       <c r="A425" t="inlineStr">
         <is>
-          <t>paysafe</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="B425" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C425" t="inlineStr">
         <is>
-          <t>Interac</t>
+          <t>Paypal</t>
         </is>
       </c>
       <c r="D425" t="inlineStr">
@@ -18933,53 +18925,61 @@
       </c>
       <c r="H425" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I425" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I425" t="inlineStr">
+        <is>
+          <t>2026-04-20 05:34:06</t>
+        </is>
+      </c>
     </row>
     <row r="426">
       <c r="A426" t="inlineStr">
         <is>
-          <t>paysafe</t>
+          <t>paypal</t>
         </is>
       </c>
       <c r="B426" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C426" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Paypal</t>
         </is>
       </c>
       <c r="D426" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E426" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F426" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G426" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H426" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I426" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I426" t="inlineStr">
+        <is>
+          <t>2026-04-14 16:59:43</t>
+        </is>
+      </c>
     </row>
     <row r="427">
       <c r="A427" t="inlineStr">
@@ -18989,32 +18989,32 @@
       </c>
       <c r="B427" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C427" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Interac</t>
         </is>
       </c>
       <c r="D427" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E427" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F427" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G427" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H427" t="inlineStr">
@@ -19037,7 +19037,7 @@
       </c>
       <c r="C428" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D428" t="inlineStr">
@@ -19080,7 +19080,7 @@
       </c>
       <c r="C429" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D429" t="inlineStr">
@@ -19118,12 +19118,12 @@
       </c>
       <c r="B430" t="inlineStr">
         <is>
-          <t>GiftCard</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C430" t="inlineStr">
         <is>
-          <t>PaySafeCard</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D430" t="inlineStr">
@@ -19143,7 +19143,7 @@
       </c>
       <c r="G430" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H430" t="inlineStr">
@@ -19161,32 +19161,32 @@
       </c>
       <c r="B431" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C431" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D431" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E431" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F431" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G431" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H431" t="inlineStr">
@@ -19204,12 +19204,12 @@
       </c>
       <c r="B432" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>GiftCard</t>
         </is>
       </c>
       <c r="C432" t="inlineStr">
         <is>
-          <t>Skrill</t>
+          <t>PaySafeCard</t>
         </is>
       </c>
       <c r="D432" t="inlineStr">
@@ -19242,17 +19242,17 @@
     <row r="433">
       <c r="A433" t="inlineStr">
         <is>
-          <t>paystack</t>
+          <t>paysafe</t>
         </is>
       </c>
       <c r="B433" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C433" t="inlineStr">
         <is>
-          <t>Eft</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D433" t="inlineStr">
@@ -19272,7 +19272,7 @@
       </c>
       <c r="G433" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H433" t="inlineStr">
@@ -19285,17 +19285,17 @@
     <row r="434">
       <c r="A434" t="inlineStr">
         <is>
-          <t>paytm</t>
+          <t>paysafe</t>
         </is>
       </c>
       <c r="B434" t="inlineStr">
         <is>
-          <t>Upi</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C434" t="inlineStr">
         <is>
-          <t>UpiCollect</t>
+          <t>Skrill</t>
         </is>
       </c>
       <c r="D434" t="inlineStr">
@@ -19315,7 +19315,7 @@
       </c>
       <c r="G434" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H434" t="inlineStr">
@@ -19328,17 +19328,17 @@
     <row r="435">
       <c r="A435" t="inlineStr">
         <is>
-          <t>paytm</t>
+          <t>paystack</t>
         </is>
       </c>
       <c r="B435" t="inlineStr">
         <is>
-          <t>Upi</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C435" t="inlineStr">
         <is>
-          <t>UpiIntent</t>
+          <t>Eft</t>
         </is>
       </c>
       <c r="D435" t="inlineStr">
@@ -19371,17 +19371,17 @@
     <row r="436">
       <c r="A436" t="inlineStr">
         <is>
-          <t>payu</t>
+          <t>paytm</t>
         </is>
       </c>
       <c r="B436" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Upi</t>
         </is>
       </c>
       <c r="C436" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>UpiCollect</t>
         </is>
       </c>
       <c r="D436" t="inlineStr">
@@ -19401,7 +19401,7 @@
       </c>
       <c r="G436" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H436" t="inlineStr">
@@ -19414,17 +19414,17 @@
     <row r="437">
       <c r="A437" t="inlineStr">
         <is>
-          <t>payu</t>
+          <t>paytm</t>
         </is>
       </c>
       <c r="B437" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Upi</t>
         </is>
       </c>
       <c r="C437" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>UpiIntent</t>
         </is>
       </c>
       <c r="D437" t="inlineStr">
@@ -19444,7 +19444,7 @@
       </c>
       <c r="G437" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H437" t="inlineStr">
@@ -19462,12 +19462,12 @@
       </c>
       <c r="B438" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C438" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D438" t="inlineStr">
@@ -19487,7 +19487,7 @@
       </c>
       <c r="G438" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H438" t="inlineStr">
@@ -19505,12 +19505,12 @@
       </c>
       <c r="B439" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C439" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D439" t="inlineStr">
@@ -19530,7 +19530,7 @@
       </c>
       <c r="G439" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H439" t="inlineStr">
@@ -19543,17 +19543,17 @@
     <row r="440">
       <c r="A440" t="inlineStr">
         <is>
-          <t>peachpayments</t>
+          <t>payu</t>
         </is>
       </c>
       <c r="B440" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C440" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D440" t="inlineStr">
@@ -19573,34 +19573,30 @@
       </c>
       <c r="G440" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H440" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I440" t="inlineStr">
-        <is>
-          <t>2026-04-08 09:39:27</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I440" t="inlineStr"/>
     </row>
     <row r="441">
       <c r="A441" t="inlineStr">
         <is>
-          <t>peachpayments</t>
+          <t>payu</t>
         </is>
       </c>
       <c r="B441" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C441" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D441" t="inlineStr">
@@ -19620,19 +19616,15 @@
       </c>
       <c r="G441" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H441" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I441" t="inlineStr">
-        <is>
-          <t>2026-04-02 08:50:31</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I441" t="inlineStr"/>
     </row>
     <row r="442">
       <c r="A442" t="inlineStr">
@@ -19642,12 +19634,12 @@
       </c>
       <c r="B442" t="inlineStr">
         <is>
-          <t>NetworkToken</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C442" t="inlineStr">
         <is>
-          <t>NetworkToken</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D442" t="inlineStr">
@@ -19672,25 +19664,29 @@
       </c>
       <c r="H442" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I442" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I442" t="inlineStr">
+        <is>
+          <t>2026-04-08 09:39:27</t>
+        </is>
+      </c>
     </row>
     <row r="443">
       <c r="A443" t="inlineStr">
         <is>
-          <t>phonepe</t>
+          <t>peachpayments</t>
         </is>
       </c>
       <c r="B443" t="inlineStr">
         <is>
-          <t>Upi</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C443" t="inlineStr">
         <is>
-          <t>UpiCollect</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D443" t="inlineStr">
@@ -19710,30 +19706,34 @@
       </c>
       <c r="G443" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H443" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I443" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I443" t="inlineStr">
+        <is>
+          <t>2026-04-02 08:50:31</t>
+        </is>
+      </c>
     </row>
     <row r="444">
       <c r="A444" t="inlineStr">
         <is>
-          <t>phonepe</t>
+          <t>peachpayments</t>
         </is>
       </c>
       <c r="B444" t="inlineStr">
         <is>
-          <t>Upi</t>
+          <t>NetworkToken</t>
         </is>
       </c>
       <c r="C444" t="inlineStr">
         <is>
-          <t>UpiIntent</t>
+          <t>NetworkToken</t>
         </is>
       </c>
       <c r="D444" t="inlineStr">
@@ -19753,7 +19753,7 @@
       </c>
       <c r="G444" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H444" t="inlineStr">
@@ -19766,17 +19766,17 @@
     <row r="445">
       <c r="A445" t="inlineStr">
         <is>
-          <t>placetopay</t>
+          <t>phonepe</t>
         </is>
       </c>
       <c r="B445" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Upi</t>
         </is>
       </c>
       <c r="C445" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>UpiCollect</t>
         </is>
       </c>
       <c r="D445" t="inlineStr">
@@ -19809,17 +19809,17 @@
     <row r="446">
       <c r="A446" t="inlineStr">
         <is>
-          <t>placetopay</t>
+          <t>phonepe</t>
         </is>
       </c>
       <c r="B446" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Upi</t>
         </is>
       </c>
       <c r="C446" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>UpiIntent</t>
         </is>
       </c>
       <c r="D446" t="inlineStr">
@@ -19852,17 +19852,17 @@
     <row r="447">
       <c r="A447" t="inlineStr">
         <is>
-          <t>plaid</t>
+          <t>placetopay</t>
         </is>
       </c>
       <c r="B447" t="inlineStr">
         <is>
-          <t>OpenBanking</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C447" t="inlineStr">
         <is>
-          <t>OpenBankingPIS</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D447" t="inlineStr">
@@ -19895,7 +19895,7 @@
     <row r="448">
       <c r="A448" t="inlineStr">
         <is>
-          <t>powertranz</t>
+          <t>placetopay</t>
         </is>
       </c>
       <c r="B448" t="inlineStr">
@@ -19905,7 +19905,7 @@
       </c>
       <c r="C448" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D448" t="inlineStr">
@@ -19925,7 +19925,7 @@
       </c>
       <c r="G448" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H448" t="inlineStr">
@@ -19938,17 +19938,17 @@
     <row r="449">
       <c r="A449" t="inlineStr">
         <is>
-          <t>powertranz</t>
+          <t>plaid</t>
         </is>
       </c>
       <c r="B449" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>OpenBanking</t>
         </is>
       </c>
       <c r="C449" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>OpenBankingPIS</t>
         </is>
       </c>
       <c r="D449" t="inlineStr">
@@ -19968,7 +19968,7 @@
       </c>
       <c r="G449" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H449" t="inlineStr">
@@ -19981,17 +19981,17 @@
     <row r="450">
       <c r="A450" t="inlineStr">
         <is>
-          <t>prophetpay</t>
+          <t>powertranz</t>
         </is>
       </c>
       <c r="B450" t="inlineStr">
         <is>
-          <t>CardRedirect</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C450" t="inlineStr">
         <is>
-          <t>CardRedirect</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D450" t="inlineStr">
@@ -20011,7 +20011,7 @@
       </c>
       <c r="G450" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H450" t="inlineStr">
@@ -20024,7 +20024,7 @@
     <row r="451">
       <c r="A451" t="inlineStr">
         <is>
-          <t>rapyd</t>
+          <t>powertranz</t>
         </is>
       </c>
       <c r="B451" t="inlineStr">
@@ -20034,7 +20034,7 @@
       </c>
       <c r="C451" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D451" t="inlineStr">
@@ -20054,7 +20054,7 @@
       </c>
       <c r="G451" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H451" t="inlineStr">
@@ -20067,17 +20067,17 @@
     <row r="452">
       <c r="A452" t="inlineStr">
         <is>
-          <t>rapyd</t>
+          <t>prophetpay</t>
         </is>
       </c>
       <c r="B452" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>CardRedirect</t>
         </is>
       </c>
       <c r="C452" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>CardRedirect</t>
         </is>
       </c>
       <c r="D452" t="inlineStr">
@@ -20115,12 +20115,12 @@
       </c>
       <c r="B453" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C453" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D453" t="inlineStr">
@@ -20158,12 +20158,12 @@
       </c>
       <c r="B454" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C454" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D454" t="inlineStr">
@@ -20196,17 +20196,17 @@
     <row r="455">
       <c r="A455" t="inlineStr">
         <is>
-          <t>razorpay</t>
+          <t>rapyd</t>
         </is>
       </c>
       <c r="B455" t="inlineStr">
         <is>
-          <t>Upi</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C455" t="inlineStr">
         <is>
-          <t>UpiCollect</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D455" t="inlineStr">
@@ -20239,17 +20239,17 @@
     <row r="456">
       <c r="A456" t="inlineStr">
         <is>
-          <t>redsys</t>
+          <t>rapyd</t>
         </is>
       </c>
       <c r="B456" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C456" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D456" t="inlineStr">
@@ -20269,34 +20269,30 @@
       </c>
       <c r="G456" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H456" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I456" t="inlineStr">
-        <is>
-          <t>2026-04-20 20:43:17</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I456" t="inlineStr"/>
     </row>
     <row r="457">
       <c r="A457" t="inlineStr">
         <is>
-          <t>redsys</t>
+          <t>razorpay</t>
         </is>
       </c>
       <c r="B457" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Upi</t>
         </is>
       </c>
       <c r="C457" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>UpiCollect</t>
         </is>
       </c>
       <c r="D457" t="inlineStr">
@@ -20316,24 +20312,20 @@
       </c>
       <c r="G457" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H457" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I457" t="inlineStr">
-        <is>
-          <t>2026-04-20 18:32:39</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I457" t="inlineStr"/>
     </row>
     <row r="458">
       <c r="A458" t="inlineStr">
         <is>
-          <t>revolv3</t>
+          <t>redsys</t>
         </is>
       </c>
       <c r="B458" t="inlineStr">
@@ -20363,20 +20355,24 @@
       </c>
       <c r="G458" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H458" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I458" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I458" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:43:17</t>
+        </is>
+      </c>
     </row>
     <row r="459">
       <c r="A459" t="inlineStr">
         <is>
-          <t>revolv3</t>
+          <t>redsys</t>
         </is>
       </c>
       <c r="B459" t="inlineStr">
@@ -20386,35 +20382,39 @@
       </c>
       <c r="C459" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D459" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E459" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F459" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G459" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H459" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I459" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I459" t="inlineStr">
+        <is>
+          <t>2026-04-20 18:32:39</t>
+        </is>
+      </c>
     </row>
     <row r="460">
       <c r="A460" t="inlineStr">
@@ -20429,7 +20429,7 @@
       </c>
       <c r="C460" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D460" t="inlineStr">
@@ -20472,7 +20472,7 @@
       </c>
       <c r="C461" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D461" t="inlineStr">
@@ -20505,17 +20505,17 @@
     <row r="462">
       <c r="A462" t="inlineStr">
         <is>
-          <t>santander</t>
+          <t>revolv3</t>
         </is>
       </c>
       <c r="B462" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C462" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D462" t="inlineStr">
@@ -20548,32 +20548,32 @@
     <row r="463">
       <c r="A463" t="inlineStr">
         <is>
-          <t>santander</t>
+          <t>revolv3</t>
         </is>
       </c>
       <c r="B463" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C463" t="inlineStr">
         <is>
-          <t>PixAutomaticoPush</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D463" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E463" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F463" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G463" t="inlineStr">
@@ -20601,22 +20601,22 @@
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>PixAutomaticoPush</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E464" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F464" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G464" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>PixAutomaticoQr</t>
+          <t>PixAutomaticoPush</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -20687,7 +20687,7 @@
       </c>
       <c r="C466" t="inlineStr">
         <is>
-          <t>PixAutomaticoQr</t>
+          <t>PixAutomaticoPush</t>
         </is>
       </c>
       <c r="D466" t="inlineStr">
@@ -20725,12 +20725,12 @@
       </c>
       <c r="B467" t="inlineStr">
         <is>
-          <t>Voucher</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>PixAutomaticoQr</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
@@ -20763,37 +20763,37 @@
     <row r="468">
       <c r="A468" t="inlineStr">
         <is>
-          <t>shift4</t>
+          <t>santander</t>
         </is>
       </c>
       <c r="B468" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C468" t="inlineStr">
         <is>
-          <t>Eps</t>
+          <t>PixAutomaticoQr</t>
         </is>
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H468" t="inlineStr">
@@ -20806,17 +20806,17 @@
     <row r="469">
       <c r="A469" t="inlineStr">
         <is>
-          <t>shift4</t>
+          <t>santander</t>
         </is>
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Voucher</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
@@ -20836,7 +20836,7 @@
       </c>
       <c r="G469" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H469" t="inlineStr">
@@ -20859,7 +20859,7 @@
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Eps</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -20940,12 +20940,12 @@
       </c>
       <c r="B472" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -20983,12 +20983,12 @@
       </c>
       <c r="B473" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -21021,7 +21021,7 @@
     <row r="474">
       <c r="A474" t="inlineStr">
         <is>
-          <t>silverflow</t>
+          <t>shift4</t>
         </is>
       </c>
       <c r="B474" t="inlineStr">
@@ -21064,7 +21064,7 @@
     <row r="475">
       <c r="A475" t="inlineStr">
         <is>
-          <t>silverflow</t>
+          <t>shift4</t>
         </is>
       </c>
       <c r="B475" t="inlineStr">
@@ -21107,7 +21107,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>silverflow</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -21150,7 +21150,7 @@
     <row r="477">
       <c r="A477" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>silverflow</t>
         </is>
       </c>
       <c r="B477" t="inlineStr">
@@ -21193,17 +21193,17 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>stax</t>
+          <t>square</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -21223,7 +21223,7 @@
       </c>
       <c r="G478" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H478" t="inlineStr">
@@ -21236,7 +21236,7 @@
     <row r="479">
       <c r="A479" t="inlineStr">
         <is>
-          <t>stax</t>
+          <t>square</t>
         </is>
       </c>
       <c r="B479" t="inlineStr">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -21284,12 +21284,12 @@
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -21322,17 +21322,17 @@
     <row r="481">
       <c r="A481" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>stax</t>
         </is>
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -21352,7 +21352,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -21365,37 +21365,37 @@
     <row r="482">
       <c r="A482" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>stax</t>
         </is>
       </c>
       <c r="B482" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E482" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F482" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G482" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H482" t="inlineStr">
@@ -21418,7 +21418,7 @@
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Bacs</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -21461,7 +21461,7 @@
       </c>
       <c r="C484" t="inlineStr">
         <is>
-          <t>Bacs</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D484" t="inlineStr">
@@ -21504,7 +21504,7 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Becs</t>
+          <t>Bacs</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
@@ -21547,7 +21547,7 @@
       </c>
       <c r="C486" t="inlineStr">
         <is>
-          <t>Becs</t>
+          <t>Bacs</t>
         </is>
       </c>
       <c r="D486" t="inlineStr">
@@ -21590,7 +21590,7 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Sepa</t>
+          <t>Becs</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
@@ -21633,7 +21633,7 @@
       </c>
       <c r="C488" t="inlineStr">
         <is>
-          <t>Sepa</t>
+          <t>Becs</t>
         </is>
       </c>
       <c r="D488" t="inlineStr">
@@ -21671,12 +21671,12 @@
       </c>
       <c r="B489" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>BancontactCard</t>
+          <t>Sepa</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
@@ -21696,19 +21696,15 @@
       </c>
       <c r="G489" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H489" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I489" t="inlineStr">
-        <is>
-          <t>2026-04-20 22:45:07</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I489" t="inlineStr"/>
     </row>
     <row r="490">
       <c r="A490" t="inlineStr">
@@ -21718,12 +21714,12 @@
       </c>
       <c r="B490" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C490" t="inlineStr">
         <is>
-          <t>BancontactCard</t>
+          <t>Sepa</t>
         </is>
       </c>
       <c r="D490" t="inlineStr">
@@ -21748,14 +21744,10 @@
       </c>
       <c r="H490" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I490" t="inlineStr">
-        <is>
-          <t>2026-04-20 22:45:07</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I490" t="inlineStr"/>
     </row>
     <row r="491">
       <c r="A491" t="inlineStr">
@@ -21770,7 +21762,7 @@
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>Blik</t>
+          <t>BancontactCard</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
@@ -21795,10 +21787,14 @@
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I491" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:45:07</t>
+        </is>
+      </c>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -21813,35 +21809,39 @@
       </c>
       <c r="C492" t="inlineStr">
         <is>
-          <t>Eps</t>
+          <t>BancontactCard</t>
         </is>
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I492" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I492" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:45:07</t>
+        </is>
+      </c>
     </row>
     <row r="493">
       <c r="A493" t="inlineStr">
@@ -21856,7 +21856,7 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>Blik</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Eps</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -21942,27 +21942,27 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E495" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F495" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G495" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H495" t="inlineStr">
@@ -21985,7 +21985,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>OnlineBankingFpx</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -22028,27 +22028,27 @@
       </c>
       <c r="C497" t="inlineStr">
         <is>
-          <t>Przelewy24</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -22071,7 +22071,7 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>OnlineBankingFpx</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
@@ -22114,27 +22114,27 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>Przelewy24</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E499" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F499" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G499" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H499" t="inlineStr">
@@ -22152,12 +22152,12 @@
       </c>
       <c r="B500" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -22195,32 +22195,32 @@
       </c>
       <c r="B501" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C501" t="inlineStr">
         <is>
-          <t>Bacs</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -22243,7 +22243,7 @@
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Multibanco</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>SepaBankTransfer</t>
+          <t>Bacs</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -22324,12 +22324,12 @@
       </c>
       <c r="B504" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Multibanco</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -22354,14 +22354,10 @@
       </c>
       <c r="H504" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I504" t="inlineStr">
-        <is>
-          <t>2026-04-21 01:34:33</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I504" t="inlineStr"/>
     </row>
     <row r="505">
       <c r="A505" t="inlineStr">
@@ -22371,27 +22367,27 @@
       </c>
       <c r="B505" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>SepaBankTransfer</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E505" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F505" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G505" t="inlineStr">
@@ -22401,14 +22397,10 @@
       </c>
       <c r="H505" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I505" t="inlineStr">
-        <is>
-          <t>2026-04-20 16:54:39</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I505" t="inlineStr"/>
     </row>
     <row r="506">
       <c r="A506" t="inlineStr">
@@ -22423,7 +22415,7 @@
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -22453,7 +22445,7 @@
       </c>
       <c r="I506" t="inlineStr">
         <is>
-          <t>2026-04-21 01:38:16</t>
+          <t>2026-04-21 01:34:33</t>
         </is>
       </c>
     </row>
@@ -22470,7 +22462,7 @@
       </c>
       <c r="C507" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D507" t="inlineStr">
@@ -22500,7 +22492,7 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>2026-04-20 10:53:25</t>
+          <t>2026-04-20 16:54:39</t>
         </is>
       </c>
     </row>
@@ -22512,12 +22504,12 @@
       </c>
       <c r="B508" t="inlineStr">
         <is>
-          <t>PayLater</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
@@ -22537,7 +22529,7 @@
       </c>
       <c r="G508" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H508" t="inlineStr">
@@ -22547,7 +22539,7 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>2026-04-21 01:37:45</t>
+          <t>2026-04-21 01:38:16</t>
         </is>
       </c>
     </row>
@@ -22559,40 +22551,44 @@
       </c>
       <c r="B509" t="inlineStr">
         <is>
-          <t>PayLater</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C509" t="inlineStr">
         <is>
-          <t>AfterpayClearpay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H509" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I509" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I509" t="inlineStr">
+        <is>
+          <t>2026-04-20 10:53:25</t>
+        </is>
+      </c>
     </row>
     <row r="510">
       <c r="A510" t="inlineStr">
@@ -22607,7 +22603,7 @@
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Klarna</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
@@ -22637,7 +22633,7 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>2026-04-21 01:36:26</t>
+          <t>2026-04-21 01:37:45</t>
         </is>
       </c>
     </row>
@@ -22649,12 +22645,12 @@
       </c>
       <c r="B511" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>PayLater</t>
         </is>
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>AliPay</t>
+          <t>AfterpayClearpay</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -22692,12 +22688,12 @@
       </c>
       <c r="B512" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>PayLater</t>
         </is>
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>AmazonPay</t>
+          <t>Klarna</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -22722,10 +22718,14 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I512" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr">
+        <is>
+          <t>2026-04-21 01:36:26</t>
+        </is>
+      </c>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -22740,22 +22740,22 @@
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>AmazonPay</t>
+          <t>AliPay</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E513" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F513" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G513" t="inlineStr">
@@ -22783,7 +22783,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>AmazonPay</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -22826,7 +22826,7 @@
       </c>
       <c r="C515" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>AmazonPay</t>
         </is>
       </c>
       <c r="D515" t="inlineStr">
@@ -22869,7 +22869,7 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>Cashapp</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
@@ -22912,7 +22912,7 @@
       </c>
       <c r="C517" t="inlineStr">
         <is>
-          <t>Cashapp</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D517" t="inlineStr">
@@ -22955,7 +22955,7 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Cashapp</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
@@ -22998,7 +22998,7 @@
       </c>
       <c r="C519" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Cashapp</t>
         </is>
       </c>
       <c r="D519" t="inlineStr">
@@ -23041,7 +23041,7 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>RevolutPay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
@@ -23084,7 +23084,7 @@
       </c>
       <c r="C521" t="inlineStr">
         <is>
-          <t>RevolutPay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D521" t="inlineStr">
@@ -23127,7 +23127,7 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>WeChatPay</t>
+          <t>RevolutPay</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
@@ -23160,37 +23160,37 @@
     <row r="523">
       <c r="A523" t="inlineStr">
         <is>
-          <t>tesouro</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="B523" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C523" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>RevolutPay</t>
         </is>
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H523" t="inlineStr">
@@ -23203,37 +23203,37 @@
     <row r="524">
       <c r="A524" t="inlineStr">
         <is>
-          <t>tesouro</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="B524" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>WeChatPay</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H524" t="inlineStr">
@@ -23256,7 +23256,7 @@
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -23299,7 +23299,7 @@
       </c>
       <c r="C526" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D526" t="inlineStr">
@@ -23337,12 +23337,12 @@
       </c>
       <c r="B527" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
@@ -23362,7 +23362,7 @@
       </c>
       <c r="G527" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H527" t="inlineStr">
@@ -23380,12 +23380,12 @@
       </c>
       <c r="B528" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C528" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D528" t="inlineStr">
@@ -23405,7 +23405,7 @@
       </c>
       <c r="G528" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H528" t="inlineStr">
@@ -23428,7 +23428,7 @@
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
@@ -23471,7 +23471,7 @@
       </c>
       <c r="C530" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D530" t="inlineStr">
@@ -23504,17 +23504,17 @@
     <row r="531">
       <c r="A531" t="inlineStr">
         <is>
-          <t>tokenio</t>
+          <t>tesouro</t>
         </is>
       </c>
       <c r="B531" t="inlineStr">
         <is>
-          <t>OpenBanking</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>OpenBankingPIS</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
@@ -23534,7 +23534,7 @@
       </c>
       <c r="G531" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H531" t="inlineStr">
@@ -23547,37 +23547,37 @@
     <row r="532">
       <c r="A532" t="inlineStr">
         <is>
-          <t>truelayer</t>
+          <t>tesouro</t>
         </is>
       </c>
       <c r="B532" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C532" t="inlineStr">
         <is>
-          <t>OpenBanking</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H532" t="inlineStr">
@@ -23590,17 +23590,17 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>trustly</t>
+          <t>tokenio</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>OpenBanking</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>Trustly</t>
+          <t>OpenBankingPIS</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
@@ -23633,7 +23633,7 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>trustpay</t>
+          <t>truelayer</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
@@ -23643,7 +23643,7 @@
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>Blik</t>
+          <t>OpenBanking</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -23663,7 +23663,7 @@
       </c>
       <c r="G534" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H534" t="inlineStr">
@@ -23676,7 +23676,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>trustpay</t>
+          <t>trustly</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -23686,7 +23686,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Eps</t>
+          <t>Trustly</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -23706,19 +23706,15 @@
       </c>
       <c r="G535" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H535" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I535" t="inlineStr">
-        <is>
-          <t>2026-04-21 00:07:05</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I535" t="inlineStr"/>
     </row>
     <row r="536">
       <c r="A536" t="inlineStr">
@@ -23733,7 +23729,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>Blik</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -23776,7 +23772,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Eps</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -23806,7 +23802,7 @@
       </c>
       <c r="I537" t="inlineStr">
         <is>
-          <t>2026-04-19 23:12:22</t>
+          <t>2026-04-21 00:07:05</t>
         </is>
       </c>
     </row>
@@ -23823,7 +23819,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -23861,12 +23857,12 @@
       </c>
       <c r="B539" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>InstantBankTransfer</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -23891,10 +23887,14 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I539" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr">
+        <is>
+          <t>2026-04-19 23:12:22</t>
+        </is>
+      </c>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -23904,12 +23904,12 @@
       </c>
       <c r="B540" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>InstantBankTransferFinland</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -23952,7 +23952,7 @@
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>InstantBankTransferPoland</t>
+          <t>InstantBankTransfer</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -23995,7 +23995,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>SepaBankTransfer</t>
+          <t>InstantBankTransferFinland</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -24020,14 +24020,10 @@
       </c>
       <c r="H542" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I542" t="inlineStr">
-        <is>
-          <t>2026-04-20 23:47:16</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I542" t="inlineStr"/>
     </row>
     <row r="543">
       <c r="A543" t="inlineStr">
@@ -24037,12 +24033,12 @@
       </c>
       <c r="B543" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>InstantBankTransferPoland</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -24067,14 +24063,10 @@
       </c>
       <c r="H543" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I543" t="inlineStr">
-        <is>
-          <t>2026-04-21 00:08:32</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I543" t="inlineStr"/>
     </row>
     <row r="544">
       <c r="A544" t="inlineStr">
@@ -24084,12 +24076,12 @@
       </c>
       <c r="B544" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>SepaBankTransfer</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -24119,7 +24111,7 @@
       </c>
       <c r="I544" t="inlineStr">
         <is>
-          <t>2026-04-21 01:17:59</t>
+          <t>2026-04-20 23:47:16</t>
         </is>
       </c>
     </row>
@@ -24131,12 +24123,12 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>NetworkToken</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>NetworkToken</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -24161,10 +24153,14 @@
       </c>
       <c r="H545" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I545" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I545" t="inlineStr">
+        <is>
+          <t>2026-04-21 00:08:32</t>
+        </is>
+      </c>
     </row>
     <row r="546">
       <c r="A546" t="inlineStr">
@@ -24174,12 +24170,12 @@
       </c>
       <c r="B546" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -24199,7 +24195,7 @@
       </c>
       <c r="G546" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H546" t="inlineStr">
@@ -24209,7 +24205,7 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>2026-04-21 01:01:59</t>
+          <t>2026-04-21 01:17:59</t>
         </is>
       </c>
     </row>
@@ -24221,12 +24217,12 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>NetworkToken</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>NetworkToken</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -24246,34 +24242,30 @@
       </c>
       <c r="G547" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I547" t="inlineStr">
-        <is>
-          <t>2026-04-20 20:43:18</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr"/>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
         <is>
-          <t>trustpayments</t>
+          <t>trustpay</t>
         </is>
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -24293,30 +24285,34 @@
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I548" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr">
+        <is>
+          <t>2026-04-21 01:01:59</t>
+        </is>
+      </c>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
         <is>
-          <t>trustpayments</t>
+          <t>trustpay</t>
         </is>
       </c>
       <c r="B549" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -24336,20 +24332,24 @@
       </c>
       <c r="G549" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H549" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I549" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I549" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:43:18</t>
+        </is>
+      </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>tsys</t>
+          <t>trustpayments</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
@@ -24392,7 +24392,7 @@
     <row r="551">
       <c r="A551" t="inlineStr">
         <is>
-          <t>tsys</t>
+          <t>trustpayments</t>
         </is>
       </c>
       <c r="B551" t="inlineStr">
@@ -24435,17 +24435,17 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>tsys</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>OpenBanking</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -24478,17 +24478,17 @@
     <row r="553">
       <c r="A553" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>tsys</t>
         </is>
       </c>
       <c r="B553" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>OpenBankingUk</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -24521,17 +24521,17 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>wellsfargo</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>OpenBanking</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -24551,7 +24551,7 @@
       </c>
       <c r="G554" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H554" t="inlineStr">
@@ -24564,17 +24564,17 @@
     <row r="555">
       <c r="A555" t="inlineStr">
         <is>
-          <t>wellsfargo</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B555" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>OpenBankingUk</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -24612,32 +24612,32 @@
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E556" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F556" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -24660,7 +24660,7 @@
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -24703,7 +24703,7 @@
       </c>
       <c r="C558" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D558" t="inlineStr">
@@ -24741,12 +24741,12 @@
       </c>
       <c r="B559" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
@@ -24766,7 +24766,7 @@
       </c>
       <c r="G559" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H559" t="inlineStr">
@@ -24784,12 +24784,12 @@
       </c>
       <c r="B560" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C560" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D560" t="inlineStr">
@@ -24809,7 +24809,7 @@
       </c>
       <c r="G560" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H560" t="inlineStr">
@@ -24832,7 +24832,7 @@
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
@@ -24875,7 +24875,7 @@
       </c>
       <c r="C562" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D562" t="inlineStr">
@@ -24908,17 +24908,17 @@
     <row r="563">
       <c r="A563" t="inlineStr">
         <is>
-          <t>worldline</t>
+          <t>wellsfargo</t>
         </is>
       </c>
       <c r="B563" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
@@ -24938,7 +24938,7 @@
       </c>
       <c r="G563" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H563" t="inlineStr">
@@ -24951,37 +24951,37 @@
     <row r="564">
       <c r="A564" t="inlineStr">
         <is>
-          <t>worldline</t>
+          <t>wellsfargo</t>
         </is>
       </c>
       <c r="B564" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C564" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H564" t="inlineStr">
@@ -24999,12 +24999,12 @@
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
@@ -25042,12 +25042,12 @@
       </c>
       <c r="B566" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -25080,7 +25080,7 @@
     <row r="567">
       <c r="A567" t="inlineStr">
         <is>
-          <t>worldpay</t>
+          <t>worldline</t>
         </is>
       </c>
       <c r="B567" t="inlineStr">
@@ -25110,24 +25110,20 @@
       </c>
       <c r="G567" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H567" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I567" t="inlineStr">
-        <is>
-          <t>2026-04-21 00:59:53</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I567" t="inlineStr"/>
     </row>
     <row r="568">
       <c r="A568" t="inlineStr">
         <is>
-          <t>worldpay</t>
+          <t>worldline</t>
         </is>
       </c>
       <c r="B568" t="inlineStr">
@@ -25137,27 +25133,27 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E568" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F568" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G568" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H568" t="inlineStr">
@@ -25180,7 +25176,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -25210,7 +25206,7 @@
       </c>
       <c r="I569" t="inlineStr">
         <is>
-          <t>2026-04-20 08:06:33</t>
+          <t>2026-04-21 00:59:53</t>
         </is>
       </c>
     </row>
@@ -25227,7 +25223,7 @@
       </c>
       <c r="C570" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D570" t="inlineStr">
@@ -25265,12 +25261,12 @@
       </c>
       <c r="B571" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
@@ -25290,7 +25286,7 @@
       </c>
       <c r="G571" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H571" t="inlineStr">
@@ -25300,7 +25296,7 @@
       </c>
       <c r="I571" t="inlineStr">
         <is>
-          <t>2026-04-19 04:54:56</t>
+          <t>2026-04-20 08:06:33</t>
         </is>
       </c>
     </row>
@@ -25312,49 +25308,45 @@
       </c>
       <c r="B572" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C572" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I572" t="inlineStr">
-        <is>
-          <t>2026-04-19 16:49:10</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr"/>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
         <is>
-          <t>worldpaymodular</t>
+          <t>worldpay</t>
         </is>
       </c>
       <c r="B573" t="inlineStr">
@@ -25384,7 +25376,7 @@
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
@@ -25394,14 +25386,14 @@
       </c>
       <c r="I573" t="inlineStr">
         <is>
-          <t>2026-01-21 11:49:57</t>
+          <t>2026-04-19 04:54:56</t>
         </is>
       </c>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
         <is>
-          <t>worldpaymodular</t>
+          <t>worldpay</t>
         </is>
       </c>
       <c r="B574" t="inlineStr">
@@ -25411,35 +25403,39 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E574" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F574" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G574" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H574" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I574" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I574" t="inlineStr">
+        <is>
+          <t>2026-04-19 16:49:10</t>
+        </is>
+      </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
@@ -25454,7 +25450,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -25484,7 +25480,7 @@
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>2026-01-21 12:08:57</t>
+          <t>2026-01-21 11:49:57</t>
         </is>
       </c>
     </row>
@@ -25501,7 +25497,7 @@
       </c>
       <c r="C576" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D576" t="inlineStr">
@@ -25534,17 +25530,17 @@
     <row r="577">
       <c r="A577" t="inlineStr">
         <is>
-          <t>worldpayvantiv</t>
+          <t>worldpaymodular</t>
         </is>
       </c>
       <c r="B577" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
@@ -25564,30 +25560,34 @@
       </c>
       <c r="G577" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I577" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr">
+        <is>
+          <t>2026-01-21 12:08:57</t>
+        </is>
+      </c>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
         <is>
-          <t>worldpayvantiv</t>
+          <t>worldpaymodular</t>
         </is>
       </c>
       <c r="B578" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C578" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D578" t="inlineStr">
@@ -25607,7 +25607,7 @@
       </c>
       <c r="G578" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H578" t="inlineStr">
@@ -25630,7 +25630,7 @@
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
@@ -25673,7 +25673,7 @@
       </c>
       <c r="C580" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="D580" t="inlineStr">
@@ -25716,7 +25716,7 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
@@ -25759,7 +25759,7 @@
       </c>
       <c r="C582" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D582" t="inlineStr">
@@ -25797,12 +25797,12 @@
       </c>
       <c r="B583" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
@@ -25822,7 +25822,7 @@
       </c>
       <c r="G583" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H583" t="inlineStr">
@@ -25840,12 +25840,12 @@
       </c>
       <c r="B584" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C584" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D584" t="inlineStr">
@@ -25865,7 +25865,7 @@
       </c>
       <c r="G584" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H584" t="inlineStr">
@@ -25888,7 +25888,7 @@
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
@@ -25931,7 +25931,7 @@
       </c>
       <c r="C586" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D586" t="inlineStr">
@@ -25964,17 +25964,17 @@
     <row r="587">
       <c r="A587" t="inlineStr">
         <is>
-          <t>worldpayxml</t>
+          <t>worldpayvantiv</t>
         </is>
       </c>
       <c r="B587" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
@@ -25994,66 +25994,58 @@
       </c>
       <c r="G587" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H587" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I587" t="inlineStr">
-        <is>
-          <t>2026-04-21 00:46:51</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I587" t="inlineStr"/>
     </row>
     <row r="588">
       <c r="A588" t="inlineStr">
         <is>
-          <t>worldpayxml</t>
+          <t>worldpayvantiv</t>
         </is>
       </c>
       <c r="B588" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C588" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H588" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I588" t="inlineStr">
-        <is>
-          <t>2026-04-20 12:19:30</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I588" t="inlineStr"/>
     </row>
     <row r="589">
       <c r="A589" t="inlineStr">
@@ -26063,12 +26055,12 @@
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
@@ -26088,7 +26080,7 @@
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
@@ -26098,7 +26090,7 @@
       </c>
       <c r="I589" t="inlineStr">
         <is>
-          <t>2026-03-20 14:37:20</t>
+          <t>2026-04-21 00:46:51</t>
         </is>
       </c>
     </row>
@@ -26110,40 +26102,44 @@
       </c>
       <c r="B590" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E590" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F590" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G590" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H590" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I590" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I590" t="inlineStr">
+        <is>
+          <t>2026-04-20 12:19:30</t>
+        </is>
+      </c>
     </row>
     <row r="591">
       <c r="A591" t="inlineStr">
@@ -26158,7 +26154,7 @@
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -26188,7 +26184,7 @@
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>2026-03-20 14:38:54</t>
+          <t>2026-03-20 14:37:20</t>
         </is>
       </c>
     </row>
@@ -26205,7 +26201,7 @@
       </c>
       <c r="C592" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D592" t="inlineStr">
@@ -26238,17 +26234,17 @@
     <row r="593">
       <c r="A593" t="inlineStr">
         <is>
-          <t>xendit</t>
+          <t>worldpayxml</t>
         </is>
       </c>
       <c r="B593" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
@@ -26268,30 +26264,34 @@
       </c>
       <c r="G593" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I593" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:38:54</t>
+        </is>
+      </c>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
         <is>
-          <t>xendit</t>
+          <t>worldpayxml</t>
         </is>
       </c>
       <c r="B594" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C594" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D594" t="inlineStr">
@@ -26311,7 +26311,7 @@
       </c>
       <c r="G594" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H594" t="inlineStr">
@@ -26334,7 +26334,7 @@
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
@@ -26377,7 +26377,7 @@
       </c>
       <c r="C596" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D596" t="inlineStr">
@@ -26415,12 +26415,12 @@
       </c>
       <c r="B597" t="inlineStr">
         <is>
-          <t>RealTimePayment</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Qris</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
@@ -26440,7 +26440,7 @@
       </c>
       <c r="G597" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H597" t="inlineStr">
@@ -26458,12 +26458,12 @@
       </c>
       <c r="B598" t="inlineStr">
         <is>
-          <t>RealTimePayment</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C598" t="inlineStr">
         <is>
-          <t>Qris</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D598" t="inlineStr">
@@ -26483,7 +26483,7 @@
       </c>
       <c r="G598" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H598" t="inlineStr">
@@ -26496,17 +26496,17 @@
     <row r="599">
       <c r="A599" t="inlineStr">
         <is>
-          <t>zen</t>
+          <t>xendit</t>
         </is>
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>RealTimePayment</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Multibanco</t>
+          <t>Qris</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
@@ -26526,7 +26526,7 @@
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -26539,37 +26539,37 @@
     <row r="600">
       <c r="A600" t="inlineStr">
         <is>
-          <t>zen</t>
+          <t>xendit</t>
         </is>
       </c>
       <c r="B600" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>RealTimePayment</t>
         </is>
       </c>
       <c r="C600" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Qris</t>
         </is>
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H600" t="inlineStr">
@@ -26592,7 +26592,7 @@
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Pse</t>
+          <t>Multibanco</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
@@ -26630,12 +26630,12 @@
       </c>
       <c r="B602" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -26673,12 +26673,12 @@
       </c>
       <c r="B603" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Pse</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -26716,12 +26716,12 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Voucher</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -26759,12 +26759,12 @@
       </c>
       <c r="B605" t="inlineStr">
         <is>
-          <t>Voucher</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Efecty</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -26807,7 +26807,7 @@
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>PagoEfectivo</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -26850,7 +26850,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>RedCompra</t>
+          <t>Efecty</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -26893,7 +26893,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>RedPagos</t>
+          <t>PagoEfectivo</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -26931,12 +26931,12 @@
       </c>
       <c r="B609" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Voucher</t>
         </is>
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>RedCompra</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -26974,12 +26974,12 @@
       </c>
       <c r="B610" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Voucher</t>
         </is>
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>RedPagos</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -27012,17 +27012,17 @@
     <row r="611">
       <c r="A611" t="inlineStr">
         <is>
-          <t>zift</t>
+          <t>zen</t>
         </is>
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -27042,54 +27042,50 @@
       </c>
       <c r="G611" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H611" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I611" t="inlineStr">
-        <is>
-          <t>2026-04-20 02:16:52</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I611" t="inlineStr"/>
     </row>
     <row r="612">
       <c r="A612" t="inlineStr">
         <is>
-          <t>zift</t>
+          <t>zen</t>
         </is>
       </c>
       <c r="B612" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E612" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F612" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G612" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H612" t="inlineStr">
@@ -27112,7 +27108,7 @@
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -27142,7 +27138,7 @@
       </c>
       <c r="I613" t="inlineStr">
         <is>
-          <t>2026-04-20 20:57:09</t>
+          <t>2026-04-20 02:16:52</t>
         </is>
       </c>
     </row>
@@ -27159,7 +27155,7 @@
       </c>
       <c r="C614" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D614" t="inlineStr">
@@ -27192,17 +27188,17 @@
     <row r="615">
       <c r="A615" t="inlineStr">
         <is>
-          <t>zsl</t>
+          <t>zift</t>
         </is>
       </c>
       <c r="B615" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>LocalBankTransfer</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
@@ -27222,55 +27218,59 @@
       </c>
       <c r="G615" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I615" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:57:09</t>
+        </is>
+      </c>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
         <is>
-          <t>adyen</t>
+          <t>zift</t>
         </is>
       </c>
       <c r="B616" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C616" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Payment (Decrypt Flow)</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>HS pre-decrypts the wallet token and sends plaintext card data to the connector instead of the encrypted blob</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="I616" t="inlineStr"/>
@@ -27278,42 +27278,42 @@
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>adyen</t>
+          <t>zsl</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>LocalBankTransfer</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Payment (Decrypt Flow)</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>HS pre-decrypts the wallet token and sends plaintext card data to the connector instead of the encrypted blob</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="I617" t="inlineStr"/>
@@ -27331,7 +27331,7 @@
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
@@ -27346,12 +27346,12 @@
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
@@ -27364,7 +27364,7 @@
     <row r="619">
       <c r="A619" t="inlineStr">
         <is>
-          <t>archipel</t>
+          <t>adyen</t>
         </is>
       </c>
       <c r="B619" t="inlineStr">
@@ -27374,7 +27374,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -27389,12 +27389,12 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H619" t="inlineStr">
@@ -27407,7 +27407,7 @@
     <row r="620">
       <c r="A620" t="inlineStr">
         <is>
-          <t>bankofamerica</t>
+          <t>adyen</t>
         </is>
       </c>
       <c r="B620" t="inlineStr">
@@ -27417,7 +27417,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -27432,12 +27432,12 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H620" t="inlineStr">
@@ -27450,7 +27450,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>bankofamerica</t>
+          <t>archipel</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -27460,7 +27460,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -27475,7 +27475,7 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
@@ -27503,7 +27503,7 @@
       </c>
       <c r="C622" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D622" t="inlineStr">
@@ -27518,7 +27518,7 @@
       </c>
       <c r="F622" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G622" t="inlineStr">
@@ -27536,7 +27536,7 @@
     <row r="623">
       <c r="A623" t="inlineStr">
         <is>
-          <t>barclaycard</t>
+          <t>bankofamerica</t>
         </is>
       </c>
       <c r="B623" t="inlineStr">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -27561,7 +27561,7 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
@@ -27579,7 +27579,7 @@
     <row r="624">
       <c r="A624" t="inlineStr">
         <is>
-          <t>barclaycard</t>
+          <t>bankofamerica</t>
         </is>
       </c>
       <c r="B624" t="inlineStr">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -27604,7 +27604,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
@@ -27632,7 +27632,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -27647,7 +27647,7 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
@@ -27665,7 +27665,7 @@
     <row r="626">
       <c r="A626" t="inlineStr">
         <is>
-          <t>braintree</t>
+          <t>barclaycard</t>
         </is>
       </c>
       <c r="B626" t="inlineStr">
@@ -27675,7 +27675,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -27690,7 +27690,7 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
@@ -27708,7 +27708,7 @@
     <row r="627">
       <c r="A627" t="inlineStr">
         <is>
-          <t>braintree</t>
+          <t>barclaycard</t>
         </is>
       </c>
       <c r="B627" t="inlineStr">
@@ -27718,7 +27718,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -27733,7 +27733,7 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
@@ -27761,7 +27761,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -27776,7 +27776,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
@@ -27794,7 +27794,7 @@
     <row r="629">
       <c r="A629" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>braintree</t>
         </is>
       </c>
       <c r="B629" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
@@ -27819,7 +27819,7 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
@@ -27837,7 +27837,7 @@
     <row r="630">
       <c r="A630" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>braintree</t>
         </is>
       </c>
       <c r="B630" t="inlineStr">
@@ -27847,7 +27847,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -27862,7 +27862,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
@@ -27890,7 +27890,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -27905,7 +27905,7 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
@@ -27923,7 +27923,7 @@
     <row r="632">
       <c r="A632" t="inlineStr">
         <is>
-          <t>cybersource</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="B632" t="inlineStr">
@@ -27933,7 +27933,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -27948,7 +27948,7 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
@@ -27966,7 +27966,7 @@
     <row r="633">
       <c r="A633" t="inlineStr">
         <is>
-          <t>cybersource</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="B633" t="inlineStr">
@@ -27976,7 +27976,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -27991,7 +27991,7 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
@@ -28019,7 +28019,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -28034,7 +28034,7 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
@@ -28052,7 +28052,7 @@
     <row r="635">
       <c r="A635" t="inlineStr">
         <is>
-          <t>finix</t>
+          <t>cybersource</t>
         </is>
       </c>
       <c r="B635" t="inlineStr">
@@ -28062,7 +28062,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -28077,7 +28077,7 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
@@ -28095,7 +28095,7 @@
     <row r="636">
       <c r="A636" t="inlineStr">
         <is>
-          <t>finix</t>
+          <t>cybersource</t>
         </is>
       </c>
       <c r="B636" t="inlineStr">
@@ -28105,7 +28105,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -28120,7 +28120,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -28148,7 +28148,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -28163,7 +28163,7 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
@@ -28181,7 +28181,7 @@
     <row r="638">
       <c r="A638" t="inlineStr">
         <is>
-          <t>fiserv</t>
+          <t>finix</t>
         </is>
       </c>
       <c r="B638" t="inlineStr">
@@ -28191,7 +28191,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -28206,7 +28206,7 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
@@ -28224,7 +28224,7 @@
     <row r="639">
       <c r="A639" t="inlineStr">
         <is>
-          <t>fiuu</t>
+          <t>finix</t>
         </is>
       </c>
       <c r="B639" t="inlineStr">
@@ -28234,7 +28234,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -28249,7 +28249,7 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
@@ -28267,7 +28267,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>fiuu</t>
+          <t>fiserv</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -28277,7 +28277,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -28292,7 +28292,7 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
@@ -28320,7 +28320,7 @@
       </c>
       <c r="C641" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D641" t="inlineStr">
@@ -28335,7 +28335,7 @@
       </c>
       <c r="F641" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G641" t="inlineStr">
@@ -28353,7 +28353,7 @@
     <row r="642">
       <c r="A642" t="inlineStr">
         <is>
-          <t>gocardless</t>
+          <t>fiuu</t>
         </is>
       </c>
       <c r="B642" t="inlineStr">
@@ -28363,7 +28363,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -28378,12 +28378,12 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H642" t="inlineStr">
@@ -28396,7 +28396,7 @@
     <row r="643">
       <c r="A643" t="inlineStr">
         <is>
-          <t>gocardless</t>
+          <t>fiuu</t>
         </is>
       </c>
       <c r="B643" t="inlineStr">
@@ -28406,7 +28406,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -28421,12 +28421,12 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H643" t="inlineStr">
@@ -28449,7 +28449,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -28464,7 +28464,7 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
@@ -28482,7 +28482,7 @@
     <row r="645">
       <c r="A645" t="inlineStr">
         <is>
-          <t>hipay</t>
+          <t>gocardless</t>
         </is>
       </c>
       <c r="B645" t="inlineStr">
@@ -28492,7 +28492,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -28507,12 +28507,12 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H645" t="inlineStr">
@@ -28525,7 +28525,7 @@
     <row r="646">
       <c r="A646" t="inlineStr">
         <is>
-          <t>hipay</t>
+          <t>gocardless</t>
         </is>
       </c>
       <c r="B646" t="inlineStr">
@@ -28535,7 +28535,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -28550,12 +28550,12 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H646" t="inlineStr">
@@ -28578,7 +28578,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -28593,7 +28593,7 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
@@ -28611,7 +28611,7 @@
     <row r="648">
       <c r="A648" t="inlineStr">
         <is>
-          <t>mollie</t>
+          <t>hipay</t>
         </is>
       </c>
       <c r="B648" t="inlineStr">
@@ -28621,7 +28621,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -28636,7 +28636,7 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
@@ -28654,7 +28654,7 @@
     <row r="649">
       <c r="A649" t="inlineStr">
         <is>
-          <t>mollie</t>
+          <t>hipay</t>
         </is>
       </c>
       <c r="B649" t="inlineStr">
@@ -28664,7 +28664,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -28679,7 +28679,7 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -28722,7 +28722,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -28740,7 +28740,7 @@
     <row r="651">
       <c r="A651" t="inlineStr">
         <is>
-          <t>nmi</t>
+          <t>mollie</t>
         </is>
       </c>
       <c r="B651" t="inlineStr">
@@ -28750,7 +28750,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -28765,7 +28765,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
@@ -28783,7 +28783,7 @@
     <row r="652">
       <c r="A652" t="inlineStr">
         <is>
-          <t>nmi</t>
+          <t>mollie</t>
         </is>
       </c>
       <c r="B652" t="inlineStr">
@@ -28793,7 +28793,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -28808,7 +28808,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
@@ -28836,7 +28836,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -28851,7 +28851,7 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
@@ -28869,7 +28869,7 @@
     <row r="654">
       <c r="A654" t="inlineStr">
         <is>
-          <t>nuvei</t>
+          <t>nmi</t>
         </is>
       </c>
       <c r="B654" t="inlineStr">
@@ -28879,7 +28879,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -28894,7 +28894,7 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
@@ -28912,7 +28912,7 @@
     <row r="655">
       <c r="A655" t="inlineStr">
         <is>
-          <t>nuvei</t>
+          <t>nmi</t>
         </is>
       </c>
       <c r="B655" t="inlineStr">
@@ -28922,7 +28922,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
@@ -28955,7 +28955,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>payme</t>
+          <t>nuvei</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -28985,7 +28985,7 @@
       </c>
       <c r="G656" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H656" t="inlineStr">
@@ -28998,7 +28998,7 @@
     <row r="657">
       <c r="A657" t="inlineStr">
         <is>
-          <t>payme</t>
+          <t>nuvei</t>
         </is>
       </c>
       <c r="B657" t="inlineStr">
@@ -29028,7 +29028,7 @@
       </c>
       <c r="G657" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H657" t="inlineStr">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -29066,7 +29066,7 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
@@ -29084,7 +29084,7 @@
     <row r="659">
       <c r="A659" t="inlineStr">
         <is>
-          <t>paysafe</t>
+          <t>payme</t>
         </is>
       </c>
       <c r="B659" t="inlineStr">
@@ -29094,7 +29094,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -29109,12 +29109,12 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H659" t="inlineStr">
@@ -29127,7 +29127,7 @@
     <row r="660">
       <c r="A660" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>payme</t>
         </is>
       </c>
       <c r="B660" t="inlineStr">
@@ -29137,7 +29137,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -29152,12 +29152,12 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H660" t="inlineStr">
@@ -29170,7 +29170,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>paysafe</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -29180,7 +29180,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -29195,7 +29195,7 @@
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
@@ -29223,7 +29223,7 @@
       </c>
       <c r="C662" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D662" t="inlineStr">
@@ -29238,7 +29238,7 @@
       </c>
       <c r="F662" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G662" t="inlineStr">
@@ -29256,7 +29256,7 @@
     <row r="663">
       <c r="A663" t="inlineStr">
         <is>
-          <t>stax</t>
+          <t>square</t>
         </is>
       </c>
       <c r="B663" t="inlineStr">
@@ -29266,7 +29266,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -29281,7 +29281,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
@@ -29299,7 +29299,7 @@
     <row r="664">
       <c r="A664" t="inlineStr">
         <is>
-          <t>stax</t>
+          <t>square</t>
         </is>
       </c>
       <c r="B664" t="inlineStr">
@@ -29309,7 +29309,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -29324,7 +29324,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -29352,7 +29352,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -29367,7 +29367,7 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
@@ -29385,7 +29385,7 @@
     <row r="666">
       <c r="A666" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>stax</t>
         </is>
       </c>
       <c r="B666" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -29428,7 +29428,7 @@
     <row r="667">
       <c r="A667" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>stax</t>
         </is>
       </c>
       <c r="B667" t="inlineStr">
@@ -29438,7 +29438,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -29453,7 +29453,7 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -29496,7 +29496,7 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -29514,7 +29514,7 @@
     <row r="669">
       <c r="A669" t="inlineStr">
         <is>
-          <t>tesouro</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="B669" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -29539,7 +29539,7 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
@@ -29557,7 +29557,7 @@
     <row r="670">
       <c r="A670" t="inlineStr">
         <is>
-          <t>tesouro</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="B670" t="inlineStr">
@@ -29567,7 +29567,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -29582,7 +29582,7 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
@@ -29600,7 +29600,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>wellsfargo</t>
+          <t>tesouro</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -29643,7 +29643,7 @@
     <row r="672">
       <c r="A672" t="inlineStr">
         <is>
-          <t>wellsfargo</t>
+          <t>tesouro</t>
         </is>
       </c>
       <c r="B672" t="inlineStr">
@@ -29696,7 +29696,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -29711,7 +29711,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
@@ -29729,7 +29729,7 @@
     <row r="674">
       <c r="A674" t="inlineStr">
         <is>
-          <t>worldpayvantiv</t>
+          <t>wellsfargo</t>
         </is>
       </c>
       <c r="B674" t="inlineStr">
@@ -29739,7 +29739,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -29754,7 +29754,7 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -29772,45 +29772,131 @@
     <row r="675">
       <c r="A675" t="inlineStr">
         <is>
+          <t>wellsfargo</t>
+        </is>
+      </c>
+      <c r="B675" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="C675" t="inlineStr">
+        <is>
+          <t>Paze</t>
+        </is>
+      </c>
+      <c r="D675" t="inlineStr">
+        <is>
+          <t>Payment (Decrypt Flow)</t>
+        </is>
+      </c>
+      <c r="E675" t="inlineStr">
+        <is>
+          <t>HS pre-decrypts the wallet token and sends plaintext card data to the connector instead of the encrypted blob</t>
+        </is>
+      </c>
+      <c r="F675" t="inlineStr">
+        <is>
+          <t>POST /payments (Paze pre-decrypted token)</t>
+        </is>
+      </c>
+      <c r="G675" t="inlineStr">
+        <is>
+          <t>not_covered</t>
+        </is>
+      </c>
+      <c r="H675" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I675" t="inlineStr"/>
+    </row>
+    <row r="676">
+      <c r="A676" t="inlineStr">
+        <is>
           <t>worldpayvantiv</t>
         </is>
       </c>
-      <c r="B675" t="inlineStr">
+      <c r="B676" t="inlineStr">
         <is>
           <t>Wallet</t>
         </is>
       </c>
-      <c r="C675" t="inlineStr">
+      <c r="C676" t="inlineStr">
+        <is>
+          <t>ApplePay</t>
+        </is>
+      </c>
+      <c r="D676" t="inlineStr">
+        <is>
+          <t>Payment (Decrypt Flow)</t>
+        </is>
+      </c>
+      <c r="E676" t="inlineStr">
+        <is>
+          <t>HS pre-decrypts the wallet token and sends plaintext card data to the connector instead of the encrypted blob</t>
+        </is>
+      </c>
+      <c r="F676" t="inlineStr">
+        <is>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
+        </is>
+      </c>
+      <c r="G676" t="inlineStr">
+        <is>
+          <t>not_covered</t>
+        </is>
+      </c>
+      <c r="H676" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I676" t="inlineStr"/>
+    </row>
+    <row r="677">
+      <c r="A677" t="inlineStr">
+        <is>
+          <t>worldpayvantiv</t>
+        </is>
+      </c>
+      <c r="B677" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="C677" t="inlineStr">
         <is>
           <t>GooglePay</t>
         </is>
       </c>
-      <c r="D675" t="inlineStr">
+      <c r="D677" t="inlineStr">
         <is>
           <t>Payment (Decrypt Flow)</t>
         </is>
       </c>
-      <c r="E675" t="inlineStr">
+      <c r="E677" t="inlineStr">
         <is>
           <t>HS pre-decrypts the wallet token and sends plaintext card data to the connector instead of the encrypted blob</t>
         </is>
       </c>
-      <c r="F675" t="inlineStr">
+      <c r="F677" t="inlineStr">
         <is>
           <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
-      <c r="G675" t="inlineStr">
+      <c r="G677" t="inlineStr">
         <is>
           <t>not_covered</t>
         </is>
       </c>
-      <c r="H675" t="inlineStr">
+      <c r="H677" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I675" t="inlineStr"/>
+      <c r="I677" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/bucket_2_connector_pm_features.xlsx
+++ b/bucket_2_connector_pm_features.xlsx
@@ -417,7 +417,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:I677"/>
+  <dimension ref="A1:I678"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="14" customWidth="1" min="1" max="1"/>
@@ -2798,7 +2798,7 @@
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H55" t="inlineStr">
@@ -2841,7 +2841,7 @@
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -20591,17 +20591,17 @@
     <row r="464">
       <c r="A464" t="inlineStr">
         <is>
-          <t>santander</t>
+          <t>sanlam</t>
         </is>
       </c>
       <c r="B464" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C464" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>EftDebitOrder</t>
         </is>
       </c>
       <c r="D464" t="inlineStr">
@@ -20644,7 +20644,7 @@
       </c>
       <c r="C465" t="inlineStr">
         <is>
-          <t>PixAutomaticoPush</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="D465" t="inlineStr">
@@ -20692,17 +20692,17 @@
       </c>
       <c r="D466" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E466" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F466" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G466" t="inlineStr">
@@ -20730,22 +20730,22 @@
       </c>
       <c r="C467" t="inlineStr">
         <is>
-          <t>PixAutomaticoQr</t>
+          <t>PixAutomaticoPush</t>
         </is>
       </c>
       <c r="D467" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E467" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F467" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G467" t="inlineStr">
@@ -20778,17 +20778,17 @@
       </c>
       <c r="D468" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E468" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F468" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G468" t="inlineStr">
@@ -20811,27 +20811,27 @@
       </c>
       <c r="B469" t="inlineStr">
         <is>
-          <t>Voucher</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C469" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>PixAutomaticoQr</t>
         </is>
       </c>
       <c r="D469" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E469" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F469" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G469" t="inlineStr">
@@ -20849,17 +20849,17 @@
     <row r="470">
       <c r="A470" t="inlineStr">
         <is>
-          <t>shift4</t>
+          <t>santander</t>
         </is>
       </c>
       <c r="B470" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Voucher</t>
         </is>
       </c>
       <c r="C470" t="inlineStr">
         <is>
-          <t>Eps</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="D470" t="inlineStr">
@@ -20879,7 +20879,7 @@
       </c>
       <c r="G470" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H470" t="inlineStr">
@@ -20902,7 +20902,7 @@
       </c>
       <c r="C471" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>Eps</t>
         </is>
       </c>
       <c r="D471" t="inlineStr">
@@ -20945,7 +20945,7 @@
       </c>
       <c r="C472" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D472" t="inlineStr">
@@ -20988,7 +20988,7 @@
       </c>
       <c r="C473" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D473" t="inlineStr">
@@ -21026,12 +21026,12 @@
       </c>
       <c r="B474" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C474" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D474" t="inlineStr">
@@ -21074,7 +21074,7 @@
       </c>
       <c r="C475" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D475" t="inlineStr">
@@ -21107,7 +21107,7 @@
     <row r="476">
       <c r="A476" t="inlineStr">
         <is>
-          <t>silverflow</t>
+          <t>shift4</t>
         </is>
       </c>
       <c r="B476" t="inlineStr">
@@ -21117,7 +21117,7 @@
       </c>
       <c r="C476" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D476" t="inlineStr">
@@ -21160,7 +21160,7 @@
       </c>
       <c r="C477" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D477" t="inlineStr">
@@ -21193,7 +21193,7 @@
     <row r="478">
       <c r="A478" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>silverflow</t>
         </is>
       </c>
       <c r="B478" t="inlineStr">
@@ -21203,7 +21203,7 @@
       </c>
       <c r="C478" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D478" t="inlineStr">
@@ -21246,7 +21246,7 @@
       </c>
       <c r="C479" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D479" t="inlineStr">
@@ -21279,17 +21279,17 @@
     <row r="480">
       <c r="A480" t="inlineStr">
         <is>
-          <t>stax</t>
+          <t>square</t>
         </is>
       </c>
       <c r="B480" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C480" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D480" t="inlineStr">
@@ -21309,7 +21309,7 @@
       </c>
       <c r="G480" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H480" t="inlineStr">
@@ -21327,12 +21327,12 @@
       </c>
       <c r="B481" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C481" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D481" t="inlineStr">
@@ -21352,7 +21352,7 @@
       </c>
       <c r="G481" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H481" t="inlineStr">
@@ -21375,7 +21375,7 @@
       </c>
       <c r="C482" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D482" t="inlineStr">
@@ -21408,17 +21408,17 @@
     <row r="483">
       <c r="A483" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>stax</t>
         </is>
       </c>
       <c r="B483" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C483" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D483" t="inlineStr">
@@ -21438,7 +21438,7 @@
       </c>
       <c r="G483" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H483" t="inlineStr">
@@ -21466,17 +21466,17 @@
       </c>
       <c r="D484" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E484" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F484" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G484" t="inlineStr">
@@ -21504,22 +21504,22 @@
       </c>
       <c r="C485" t="inlineStr">
         <is>
-          <t>Bacs</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D485" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E485" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F485" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G485" t="inlineStr">
@@ -21552,17 +21552,17 @@
       </c>
       <c r="D486" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E486" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F486" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G486" t="inlineStr">
@@ -21590,22 +21590,22 @@
       </c>
       <c r="C487" t="inlineStr">
         <is>
-          <t>Becs</t>
+          <t>Bacs</t>
         </is>
       </c>
       <c r="D487" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E487" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F487" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G487" t="inlineStr">
@@ -21638,17 +21638,17 @@
       </c>
       <c r="D488" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E488" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F488" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G488" t="inlineStr">
@@ -21676,22 +21676,22 @@
       </c>
       <c r="C489" t="inlineStr">
         <is>
-          <t>Sepa</t>
+          <t>Becs</t>
         </is>
       </c>
       <c r="D489" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E489" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F489" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G489" t="inlineStr">
@@ -21724,17 +21724,17 @@
       </c>
       <c r="D490" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E490" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F490" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G490" t="inlineStr">
@@ -21757,44 +21757,40 @@
       </c>
       <c r="B491" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C491" t="inlineStr">
         <is>
-          <t>BancontactCard</t>
+          <t>Sepa</t>
         </is>
       </c>
       <c r="D491" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E491" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F491" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G491" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H491" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I491" t="inlineStr">
-        <is>
-          <t>2026-04-20 22:45:07</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I491" t="inlineStr"/>
     </row>
     <row r="492">
       <c r="A492" t="inlineStr">
@@ -21814,22 +21810,22 @@
       </c>
       <c r="D492" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E492" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F492" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G492" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H492" t="inlineStr">
@@ -21856,35 +21852,39 @@
       </c>
       <c r="C493" t="inlineStr">
         <is>
-          <t>Blik</t>
+          <t>BancontactCard</t>
         </is>
       </c>
       <c r="D493" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E493" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F493" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G493" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H493" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I493" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I493" t="inlineStr">
+        <is>
+          <t>2026-04-20 22:45:07</t>
+        </is>
+      </c>
     </row>
     <row r="494">
       <c r="A494" t="inlineStr">
@@ -21899,7 +21899,7 @@
       </c>
       <c r="C494" t="inlineStr">
         <is>
-          <t>Eps</t>
+          <t>Blik</t>
         </is>
       </c>
       <c r="D494" t="inlineStr">
@@ -21942,7 +21942,7 @@
       </c>
       <c r="C495" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>Eps</t>
         </is>
       </c>
       <c r="D495" t="inlineStr">
@@ -21985,7 +21985,7 @@
       </c>
       <c r="C496" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D496" t="inlineStr">
@@ -22033,22 +22033,22 @@
       </c>
       <c r="D497" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E497" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F497" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G497" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H497" t="inlineStr">
@@ -22071,27 +22071,27 @@
       </c>
       <c r="C498" t="inlineStr">
         <is>
-          <t>OnlineBankingFpx</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D498" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E498" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F498" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G498" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H498" t="inlineStr">
@@ -22114,7 +22114,7 @@
       </c>
       <c r="C499" t="inlineStr">
         <is>
-          <t>Przelewy24</t>
+          <t>OnlineBankingFpx</t>
         </is>
       </c>
       <c r="D499" t="inlineStr">
@@ -22157,7 +22157,7 @@
       </c>
       <c r="C500" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>Przelewy24</t>
         </is>
       </c>
       <c r="D500" t="inlineStr">
@@ -22205,22 +22205,22 @@
       </c>
       <c r="D501" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E501" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F501" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G501" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H501" t="inlineStr">
@@ -22238,32 +22238,32 @@
       </c>
       <c r="B502" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C502" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D502" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E502" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F502" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G502" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H502" t="inlineStr">
@@ -22286,7 +22286,7 @@
       </c>
       <c r="C503" t="inlineStr">
         <is>
-          <t>Bacs</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D503" t="inlineStr">
@@ -22329,7 +22329,7 @@
       </c>
       <c r="C504" t="inlineStr">
         <is>
-          <t>Multibanco</t>
+          <t>Bacs</t>
         </is>
       </c>
       <c r="D504" t="inlineStr">
@@ -22372,7 +22372,7 @@
       </c>
       <c r="C505" t="inlineStr">
         <is>
-          <t>SepaBankTransfer</t>
+          <t>Multibanco</t>
         </is>
       </c>
       <c r="D505" t="inlineStr">
@@ -22410,12 +22410,12 @@
       </c>
       <c r="B506" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C506" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>SepaBankTransfer</t>
         </is>
       </c>
       <c r="D506" t="inlineStr">
@@ -22440,14 +22440,10 @@
       </c>
       <c r="H506" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I506" t="inlineStr">
-        <is>
-          <t>2026-04-21 01:34:33</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I506" t="inlineStr"/>
     </row>
     <row r="507">
       <c r="A507" t="inlineStr">
@@ -22467,17 +22463,17 @@
       </c>
       <c r="D507" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E507" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F507" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G507" t="inlineStr">
@@ -22492,7 +22488,7 @@
       </c>
       <c r="I507" t="inlineStr">
         <is>
-          <t>2026-04-20 16:54:39</t>
+          <t>2026-04-21 01:34:33</t>
         </is>
       </c>
     </row>
@@ -22509,22 +22505,22 @@
       </c>
       <c r="C508" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D508" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E508" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F508" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G508" t="inlineStr">
@@ -22539,7 +22535,7 @@
       </c>
       <c r="I508" t="inlineStr">
         <is>
-          <t>2026-04-21 01:38:16</t>
+          <t>2026-04-20 16:54:39</t>
         </is>
       </c>
     </row>
@@ -22561,17 +22557,17 @@
       </c>
       <c r="D509" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E509" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F509" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G509" t="inlineStr">
@@ -22586,7 +22582,7 @@
       </c>
       <c r="I509" t="inlineStr">
         <is>
-          <t>2026-04-20 10:53:25</t>
+          <t>2026-04-21 01:38:16</t>
         </is>
       </c>
     </row>
@@ -22598,32 +22594,32 @@
       </c>
       <c r="B510" t="inlineStr">
         <is>
-          <t>PayLater</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C510" t="inlineStr">
         <is>
-          <t>Affirm</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D510" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E510" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F510" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G510" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H510" t="inlineStr">
@@ -22633,7 +22629,7 @@
       </c>
       <c r="I510" t="inlineStr">
         <is>
-          <t>2026-04-21 01:37:45</t>
+          <t>2026-04-20 10:53:25</t>
         </is>
       </c>
     </row>
@@ -22650,7 +22646,7 @@
       </c>
       <c r="C511" t="inlineStr">
         <is>
-          <t>AfterpayClearpay</t>
+          <t>Affirm</t>
         </is>
       </c>
       <c r="D511" t="inlineStr">
@@ -22675,10 +22671,14 @@
       </c>
       <c r="H511" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I511" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I511" t="inlineStr">
+        <is>
+          <t>2026-04-21 01:37:45</t>
+        </is>
+      </c>
     </row>
     <row r="512">
       <c r="A512" t="inlineStr">
@@ -22693,7 +22693,7 @@
       </c>
       <c r="C512" t="inlineStr">
         <is>
-          <t>Klarna</t>
+          <t>AfterpayClearpay</t>
         </is>
       </c>
       <c r="D512" t="inlineStr">
@@ -22718,14 +22718,10 @@
       </c>
       <c r="H512" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I512" t="inlineStr">
-        <is>
-          <t>2026-04-21 01:36:26</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I512" t="inlineStr"/>
     </row>
     <row r="513">
       <c r="A513" t="inlineStr">
@@ -22735,12 +22731,12 @@
       </c>
       <c r="B513" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>PayLater</t>
         </is>
       </c>
       <c r="C513" t="inlineStr">
         <is>
-          <t>AliPay</t>
+          <t>Klarna</t>
         </is>
       </c>
       <c r="D513" t="inlineStr">
@@ -22765,10 +22761,14 @@
       </c>
       <c r="H513" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I513" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I513" t="inlineStr">
+        <is>
+          <t>2026-04-21 01:36:26</t>
+        </is>
+      </c>
     </row>
     <row r="514">
       <c r="A514" t="inlineStr">
@@ -22783,7 +22783,7 @@
       </c>
       <c r="C514" t="inlineStr">
         <is>
-          <t>AmazonPay</t>
+          <t>AliPay</t>
         </is>
       </c>
       <c r="D514" t="inlineStr">
@@ -22831,17 +22831,17 @@
       </c>
       <c r="D515" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E515" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F515" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G515" t="inlineStr">
@@ -22869,22 +22869,22 @@
       </c>
       <c r="C516" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>AmazonPay</t>
         </is>
       </c>
       <c r="D516" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E516" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F516" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G516" t="inlineStr">
@@ -22917,17 +22917,17 @@
       </c>
       <c r="D517" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E517" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F517" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G517" t="inlineStr">
@@ -22955,22 +22955,22 @@
       </c>
       <c r="C518" t="inlineStr">
         <is>
-          <t>Cashapp</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D518" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E518" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F518" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G518" t="inlineStr">
@@ -23003,17 +23003,17 @@
       </c>
       <c r="D519" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E519" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F519" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G519" t="inlineStr">
@@ -23041,22 +23041,22 @@
       </c>
       <c r="C520" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>Cashapp</t>
         </is>
       </c>
       <c r="D520" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E520" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F520" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G520" t="inlineStr">
@@ -23089,17 +23089,17 @@
       </c>
       <c r="D521" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E521" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F521" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G521" t="inlineStr">
@@ -23127,22 +23127,22 @@
       </c>
       <c r="C522" t="inlineStr">
         <is>
-          <t>RevolutPay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D522" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E522" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F522" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G522" t="inlineStr">
@@ -23175,17 +23175,17 @@
       </c>
       <c r="D523" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E523" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F523" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G523" t="inlineStr">
@@ -23213,22 +23213,22 @@
       </c>
       <c r="C524" t="inlineStr">
         <is>
-          <t>WeChatPay</t>
+          <t>RevolutPay</t>
         </is>
       </c>
       <c r="D524" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E524" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F524" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G524" t="inlineStr">
@@ -23246,17 +23246,17 @@
     <row r="525">
       <c r="A525" t="inlineStr">
         <is>
-          <t>tesouro</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="B525" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C525" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>WeChatPay</t>
         </is>
       </c>
       <c r="D525" t="inlineStr">
@@ -23276,7 +23276,7 @@
       </c>
       <c r="G525" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H525" t="inlineStr">
@@ -23304,17 +23304,17 @@
       </c>
       <c r="D526" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E526" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F526" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G526" t="inlineStr">
@@ -23342,22 +23342,22 @@
       </c>
       <c r="C527" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D527" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E527" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F527" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G527" t="inlineStr">
@@ -23390,17 +23390,17 @@
       </c>
       <c r="D528" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E528" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F528" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G528" t="inlineStr">
@@ -23423,32 +23423,32 @@
       </c>
       <c r="B529" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C529" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D529" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E529" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F529" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G529" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H529" t="inlineStr">
@@ -23476,17 +23476,17 @@
       </c>
       <c r="D530" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E530" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F530" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G530" t="inlineStr">
@@ -23514,22 +23514,22 @@
       </c>
       <c r="C531" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D531" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E531" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F531" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G531" t="inlineStr">
@@ -23562,17 +23562,17 @@
       </c>
       <c r="D532" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E532" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F532" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G532" t="inlineStr">
@@ -23590,37 +23590,37 @@
     <row r="533">
       <c r="A533" t="inlineStr">
         <is>
-          <t>tokenio</t>
+          <t>tesouro</t>
         </is>
       </c>
       <c r="B533" t="inlineStr">
         <is>
-          <t>OpenBanking</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C533" t="inlineStr">
         <is>
-          <t>OpenBankingPIS</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D533" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E533" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F533" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G533" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H533" t="inlineStr">
@@ -23633,17 +23633,17 @@
     <row r="534">
       <c r="A534" t="inlineStr">
         <is>
-          <t>truelayer</t>
+          <t>tokenio</t>
         </is>
       </c>
       <c r="B534" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>OpenBanking</t>
         </is>
       </c>
       <c r="C534" t="inlineStr">
         <is>
-          <t>OpenBanking</t>
+          <t>OpenBankingPIS</t>
         </is>
       </c>
       <c r="D534" t="inlineStr">
@@ -23676,7 +23676,7 @@
     <row r="535">
       <c r="A535" t="inlineStr">
         <is>
-          <t>trustly</t>
+          <t>truelayer</t>
         </is>
       </c>
       <c r="B535" t="inlineStr">
@@ -23686,7 +23686,7 @@
       </c>
       <c r="C535" t="inlineStr">
         <is>
-          <t>Trustly</t>
+          <t>OpenBanking</t>
         </is>
       </c>
       <c r="D535" t="inlineStr">
@@ -23719,7 +23719,7 @@
     <row r="536">
       <c r="A536" t="inlineStr">
         <is>
-          <t>trustpay</t>
+          <t>trustly</t>
         </is>
       </c>
       <c r="B536" t="inlineStr">
@@ -23729,7 +23729,7 @@
       </c>
       <c r="C536" t="inlineStr">
         <is>
-          <t>Blik</t>
+          <t>Trustly</t>
         </is>
       </c>
       <c r="D536" t="inlineStr">
@@ -23749,7 +23749,7 @@
       </c>
       <c r="G536" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H536" t="inlineStr">
@@ -23772,7 +23772,7 @@
       </c>
       <c r="C537" t="inlineStr">
         <is>
-          <t>Eps</t>
+          <t>Blik</t>
         </is>
       </c>
       <c r="D537" t="inlineStr">
@@ -23797,14 +23797,10 @@
       </c>
       <c r="H537" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I537" t="inlineStr">
-        <is>
-          <t>2026-04-21 00:07:05</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I537" t="inlineStr"/>
     </row>
     <row r="538">
       <c r="A538" t="inlineStr">
@@ -23819,7 +23815,7 @@
       </c>
       <c r="C538" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>Eps</t>
         </is>
       </c>
       <c r="D538" t="inlineStr">
@@ -23844,10 +23840,14 @@
       </c>
       <c r="H538" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I538" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I538" t="inlineStr">
+        <is>
+          <t>2026-04-21 00:07:05</t>
+        </is>
+      </c>
     </row>
     <row r="539">
       <c r="A539" t="inlineStr">
@@ -23862,7 +23862,7 @@
       </c>
       <c r="C539" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D539" t="inlineStr">
@@ -23887,14 +23887,10 @@
       </c>
       <c r="H539" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I539" t="inlineStr">
-        <is>
-          <t>2026-04-19 23:12:22</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I539" t="inlineStr"/>
     </row>
     <row r="540">
       <c r="A540" t="inlineStr">
@@ -23909,7 +23905,7 @@
       </c>
       <c r="C540" t="inlineStr">
         <is>
-          <t>Sofort</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D540" t="inlineStr">
@@ -23934,10 +23930,14 @@
       </c>
       <c r="H540" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I540" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I540" t="inlineStr">
+        <is>
+          <t>2026-04-19 23:12:22</t>
+        </is>
+      </c>
     </row>
     <row r="541">
       <c r="A541" t="inlineStr">
@@ -23947,12 +23947,12 @@
       </c>
       <c r="B541" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C541" t="inlineStr">
         <is>
-          <t>InstantBankTransfer</t>
+          <t>Sofort</t>
         </is>
       </c>
       <c r="D541" t="inlineStr">
@@ -23995,7 +23995,7 @@
       </c>
       <c r="C542" t="inlineStr">
         <is>
-          <t>InstantBankTransferFinland</t>
+          <t>InstantBankTransfer</t>
         </is>
       </c>
       <c r="D542" t="inlineStr">
@@ -24038,7 +24038,7 @@
       </c>
       <c r="C543" t="inlineStr">
         <is>
-          <t>InstantBankTransferPoland</t>
+          <t>InstantBankTransferFinland</t>
         </is>
       </c>
       <c r="D543" t="inlineStr">
@@ -24081,7 +24081,7 @@
       </c>
       <c r="C544" t="inlineStr">
         <is>
-          <t>SepaBankTransfer</t>
+          <t>InstantBankTransferPoland</t>
         </is>
       </c>
       <c r="D544" t="inlineStr">
@@ -24106,14 +24106,10 @@
       </c>
       <c r="H544" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I544" t="inlineStr">
-        <is>
-          <t>2026-04-20 23:47:16</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I544" t="inlineStr"/>
     </row>
     <row r="545">
       <c r="A545" t="inlineStr">
@@ -24123,12 +24119,12 @@
       </c>
       <c r="B545" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C545" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>SepaBankTransfer</t>
         </is>
       </c>
       <c r="D545" t="inlineStr">
@@ -24158,7 +24154,7 @@
       </c>
       <c r="I545" t="inlineStr">
         <is>
-          <t>2026-04-21 00:08:32</t>
+          <t>2026-04-20 23:47:16</t>
         </is>
       </c>
     </row>
@@ -24175,7 +24171,7 @@
       </c>
       <c r="C546" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D546" t="inlineStr">
@@ -24205,7 +24201,7 @@
       </c>
       <c r="I546" t="inlineStr">
         <is>
-          <t>2026-04-21 01:17:59</t>
+          <t>2026-04-21 00:08:32</t>
         </is>
       </c>
     </row>
@@ -24217,12 +24213,12 @@
       </c>
       <c r="B547" t="inlineStr">
         <is>
-          <t>NetworkToken</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C547" t="inlineStr">
         <is>
-          <t>NetworkToken</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D547" t="inlineStr">
@@ -24247,10 +24243,14 @@
       </c>
       <c r="H547" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I547" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I547" t="inlineStr">
+        <is>
+          <t>2026-04-21 01:17:59</t>
+        </is>
+      </c>
     </row>
     <row r="548">
       <c r="A548" t="inlineStr">
@@ -24260,12 +24260,12 @@
       </c>
       <c r="B548" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>NetworkToken</t>
         </is>
       </c>
       <c r="C548" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>NetworkToken</t>
         </is>
       </c>
       <c r="D548" t="inlineStr">
@@ -24285,19 +24285,15 @@
       </c>
       <c r="G548" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H548" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I548" t="inlineStr">
-        <is>
-          <t>2026-04-21 01:01:59</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I548" t="inlineStr"/>
     </row>
     <row r="549">
       <c r="A549" t="inlineStr">
@@ -24312,7 +24308,7 @@
       </c>
       <c r="C549" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D549" t="inlineStr">
@@ -24342,24 +24338,24 @@
       </c>
       <c r="I549" t="inlineStr">
         <is>
-          <t>2026-04-20 20:43:18</t>
+          <t>2026-04-21 01:01:59</t>
         </is>
       </c>
     </row>
     <row r="550">
       <c r="A550" t="inlineStr">
         <is>
-          <t>trustpayments</t>
+          <t>trustpay</t>
         </is>
       </c>
       <c r="B550" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C550" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D550" t="inlineStr">
@@ -24379,15 +24375,19 @@
       </c>
       <c r="G550" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H550" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I550" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I550" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:43:18</t>
+        </is>
+      </c>
     </row>
     <row r="551">
       <c r="A551" t="inlineStr">
@@ -24402,7 +24402,7 @@
       </c>
       <c r="C551" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D551" t="inlineStr">
@@ -24435,7 +24435,7 @@
     <row r="552">
       <c r="A552" t="inlineStr">
         <is>
-          <t>tsys</t>
+          <t>trustpayments</t>
         </is>
       </c>
       <c r="B552" t="inlineStr">
@@ -24445,7 +24445,7 @@
       </c>
       <c r="C552" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D552" t="inlineStr">
@@ -24488,7 +24488,7 @@
       </c>
       <c r="C553" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D553" t="inlineStr">
@@ -24521,17 +24521,17 @@
     <row r="554">
       <c r="A554" t="inlineStr">
         <is>
-          <t>volt</t>
+          <t>tsys</t>
         </is>
       </c>
       <c r="B554" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C554" t="inlineStr">
         <is>
-          <t>OpenBanking</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D554" t="inlineStr">
@@ -24574,7 +24574,7 @@
       </c>
       <c r="C555" t="inlineStr">
         <is>
-          <t>OpenBankingUk</t>
+          <t>OpenBanking</t>
         </is>
       </c>
       <c r="D555" t="inlineStr">
@@ -24607,17 +24607,17 @@
     <row r="556">
       <c r="A556" t="inlineStr">
         <is>
-          <t>wellsfargo</t>
+          <t>volt</t>
         </is>
       </c>
       <c r="B556" t="inlineStr">
         <is>
-          <t>BankDebit</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C556" t="inlineStr">
         <is>
-          <t>Ach</t>
+          <t>OpenBankingUk</t>
         </is>
       </c>
       <c r="D556" t="inlineStr">
@@ -24637,7 +24637,7 @@
       </c>
       <c r="G556" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H556" t="inlineStr">
@@ -24655,12 +24655,12 @@
       </c>
       <c r="B557" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankDebit</t>
         </is>
       </c>
       <c r="C557" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Ach</t>
         </is>
       </c>
       <c r="D557" t="inlineStr">
@@ -24680,7 +24680,7 @@
       </c>
       <c r="G557" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H557" t="inlineStr">
@@ -24708,17 +24708,17 @@
       </c>
       <c r="D558" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E558" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F558" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G558" t="inlineStr">
@@ -24746,22 +24746,22 @@
       </c>
       <c r="C559" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D559" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E559" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F559" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G559" t="inlineStr">
@@ -24794,17 +24794,17 @@
       </c>
       <c r="D560" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E560" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F560" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G560" t="inlineStr">
@@ -24827,32 +24827,32 @@
       </c>
       <c r="B561" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C561" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D561" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E561" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F561" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G561" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H561" t="inlineStr">
@@ -24880,17 +24880,17 @@
       </c>
       <c r="D562" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E562" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F562" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G562" t="inlineStr">
@@ -24918,22 +24918,22 @@
       </c>
       <c r="C563" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D563" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E563" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F563" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G563" t="inlineStr">
@@ -24966,17 +24966,17 @@
       </c>
       <c r="D564" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E564" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F564" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G564" t="inlineStr">
@@ -24994,37 +24994,37 @@
     <row r="565">
       <c r="A565" t="inlineStr">
         <is>
-          <t>worldline</t>
+          <t>wellsfargo</t>
         </is>
       </c>
       <c r="B565" t="inlineStr">
         <is>
-          <t>BankRedirect</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C565" t="inlineStr">
         <is>
-          <t>Giropay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D565" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E565" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F565" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G565" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H565" t="inlineStr">
@@ -25047,7 +25047,7 @@
       </c>
       <c r="C566" t="inlineStr">
         <is>
-          <t>Ideal</t>
+          <t>Giropay</t>
         </is>
       </c>
       <c r="D566" t="inlineStr">
@@ -25085,12 +25085,12 @@
       </c>
       <c r="B567" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankRedirect</t>
         </is>
       </c>
       <c r="C567" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Ideal</t>
         </is>
       </c>
       <c r="D567" t="inlineStr">
@@ -25133,7 +25133,7 @@
       </c>
       <c r="C568" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D568" t="inlineStr">
@@ -25166,7 +25166,7 @@
     <row r="569">
       <c r="A569" t="inlineStr">
         <is>
-          <t>worldpay</t>
+          <t>worldline</t>
         </is>
       </c>
       <c r="B569" t="inlineStr">
@@ -25176,7 +25176,7 @@
       </c>
       <c r="C569" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D569" t="inlineStr">
@@ -25196,19 +25196,15 @@
       </c>
       <c r="G569" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H569" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I569" t="inlineStr">
-        <is>
-          <t>2026-04-21 00:59:53</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I569" t="inlineStr"/>
     </row>
     <row r="570">
       <c r="A570" t="inlineStr">
@@ -25228,17 +25224,17 @@
       </c>
       <c r="D570" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E570" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F570" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G570" t="inlineStr">
@@ -25248,10 +25244,14 @@
       </c>
       <c r="H570" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I570" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I570" t="inlineStr">
+        <is>
+          <t>2026-04-21 00:59:53</t>
+        </is>
+      </c>
     </row>
     <row r="571">
       <c r="A571" t="inlineStr">
@@ -25266,22 +25266,22 @@
       </c>
       <c r="C571" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D571" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E571" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F571" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G571" t="inlineStr">
@@ -25291,14 +25291,10 @@
       </c>
       <c r="H571" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I571" t="inlineStr">
-        <is>
-          <t>2026-04-20 08:06:33</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I571" t="inlineStr"/>
     </row>
     <row r="572">
       <c r="A572" t="inlineStr">
@@ -25318,17 +25314,17 @@
       </c>
       <c r="D572" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E572" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F572" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G572" t="inlineStr">
@@ -25338,10 +25334,14 @@
       </c>
       <c r="H572" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I572" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I572" t="inlineStr">
+        <is>
+          <t>2026-04-20 08:06:33</t>
+        </is>
+      </c>
     </row>
     <row r="573">
       <c r="A573" t="inlineStr">
@@ -25351,44 +25351,40 @@
       </c>
       <c r="B573" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C573" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D573" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E573" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F573" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G573" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H573" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I573" t="inlineStr">
-        <is>
-          <t>2026-04-19 04:54:56</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I573" t="inlineStr"/>
     </row>
     <row r="574">
       <c r="A574" t="inlineStr">
@@ -25403,7 +25399,7 @@
       </c>
       <c r="C574" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D574" t="inlineStr">
@@ -25433,14 +25429,14 @@
       </c>
       <c r="I574" t="inlineStr">
         <is>
-          <t>2026-04-19 16:49:10</t>
+          <t>2026-04-19 04:54:56</t>
         </is>
       </c>
     </row>
     <row r="575">
       <c r="A575" t="inlineStr">
         <is>
-          <t>worldpaymodular</t>
+          <t>worldpay</t>
         </is>
       </c>
       <c r="B575" t="inlineStr">
@@ -25450,7 +25446,7 @@
       </c>
       <c r="C575" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D575" t="inlineStr">
@@ -25470,7 +25466,7 @@
       </c>
       <c r="G575" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H575" t="inlineStr">
@@ -25480,7 +25476,7 @@
       </c>
       <c r="I575" t="inlineStr">
         <is>
-          <t>2026-01-21 11:49:57</t>
+          <t>2026-04-19 16:49:10</t>
         </is>
       </c>
     </row>
@@ -25502,17 +25498,17 @@
       </c>
       <c r="D576" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E576" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F576" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G576" t="inlineStr">
@@ -25522,10 +25518,14 @@
       </c>
       <c r="H576" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I576" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I576" t="inlineStr">
+        <is>
+          <t>2026-01-21 11:49:57</t>
+        </is>
+      </c>
     </row>
     <row r="577">
       <c r="A577" t="inlineStr">
@@ -25540,22 +25540,22 @@
       </c>
       <c r="C577" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D577" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E577" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F577" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G577" t="inlineStr">
@@ -25565,14 +25565,10 @@
       </c>
       <c r="H577" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I577" t="inlineStr">
-        <is>
-          <t>2026-01-21 12:08:57</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I577" t="inlineStr"/>
     </row>
     <row r="578">
       <c r="A578" t="inlineStr">
@@ -25592,17 +25588,17 @@
       </c>
       <c r="D578" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E578" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F578" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G578" t="inlineStr">
@@ -25612,45 +25608,49 @@
       </c>
       <c r="H578" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I578" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I578" t="inlineStr">
+        <is>
+          <t>2026-01-21 12:08:57</t>
+        </is>
+      </c>
     </row>
     <row r="579">
       <c r="A579" t="inlineStr">
         <is>
-          <t>worldpayvantiv</t>
+          <t>worldpaymodular</t>
         </is>
       </c>
       <c r="B579" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C579" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D579" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E579" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F579" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G579" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H579" t="inlineStr">
@@ -25678,17 +25678,17 @@
       </c>
       <c r="D580" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E580" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F580" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G580" t="inlineStr">
@@ -25716,22 +25716,22 @@
       </c>
       <c r="C581" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="D581" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E581" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F581" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G581" t="inlineStr">
@@ -25764,17 +25764,17 @@
       </c>
       <c r="D582" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E582" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F582" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G582" t="inlineStr">
@@ -25802,22 +25802,22 @@
       </c>
       <c r="C583" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D583" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E583" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F583" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G583" t="inlineStr">
@@ -25850,17 +25850,17 @@
       </c>
       <c r="D584" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E584" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F584" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G584" t="inlineStr">
@@ -25883,32 +25883,32 @@
       </c>
       <c r="B585" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C585" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D585" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E585" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F585" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G585" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H585" t="inlineStr">
@@ -25936,17 +25936,17 @@
       </c>
       <c r="D586" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E586" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F586" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G586" t="inlineStr">
@@ -25974,22 +25974,22 @@
       </c>
       <c r="C587" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D587" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E587" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F587" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G587" t="inlineStr">
@@ -26022,17 +26022,17 @@
       </c>
       <c r="D588" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E588" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F588" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G588" t="inlineStr">
@@ -26050,49 +26050,45 @@
     <row r="589">
       <c r="A589" t="inlineStr">
         <is>
-          <t>worldpayxml</t>
+          <t>worldpayvantiv</t>
         </is>
       </c>
       <c r="B589" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C589" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D589" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E589" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F589" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G589" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H589" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I589" t="inlineStr">
-        <is>
-          <t>2026-04-21 00:46:51</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I589" t="inlineStr"/>
     </row>
     <row r="590">
       <c r="A590" t="inlineStr">
@@ -26107,7 +26103,7 @@
       </c>
       <c r="C590" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D590" t="inlineStr">
@@ -26137,7 +26133,7 @@
       </c>
       <c r="I590" t="inlineStr">
         <is>
-          <t>2026-04-20 12:19:30</t>
+          <t>2026-04-21 00:46:51</t>
         </is>
       </c>
     </row>
@@ -26149,12 +26145,12 @@
       </c>
       <c r="B591" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C591" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D591" t="inlineStr">
@@ -26174,7 +26170,7 @@
       </c>
       <c r="G591" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H591" t="inlineStr">
@@ -26184,7 +26180,7 @@
       </c>
       <c r="I591" t="inlineStr">
         <is>
-          <t>2026-03-20 14:37:20</t>
+          <t>2026-04-20 12:19:30</t>
         </is>
       </c>
     </row>
@@ -26206,17 +26202,17 @@
       </c>
       <c r="D592" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E592" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F592" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G592" t="inlineStr">
@@ -26226,10 +26222,14 @@
       </c>
       <c r="H592" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I592" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I592" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:37:20</t>
+        </is>
+      </c>
     </row>
     <row r="593">
       <c r="A593" t="inlineStr">
@@ -26244,22 +26244,22 @@
       </c>
       <c r="C593" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D593" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E593" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F593" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G593" t="inlineStr">
@@ -26269,14 +26269,10 @@
       </c>
       <c r="H593" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I593" t="inlineStr">
-        <is>
-          <t>2026-03-20 14:38:54</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I593" t="inlineStr"/>
     </row>
     <row r="594">
       <c r="A594" t="inlineStr">
@@ -26296,17 +26292,17 @@
       </c>
       <c r="D594" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E594" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F594" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G594" t="inlineStr">
@@ -26316,45 +26312,49 @@
       </c>
       <c r="H594" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I594" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I594" t="inlineStr">
+        <is>
+          <t>2026-03-20 14:38:54</t>
+        </is>
+      </c>
     </row>
     <row r="595">
       <c r="A595" t="inlineStr">
         <is>
-          <t>xendit</t>
+          <t>worldpayxml</t>
         </is>
       </c>
       <c r="B595" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C595" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D595" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E595" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F595" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G595" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H595" t="inlineStr">
@@ -26382,17 +26382,17 @@
       </c>
       <c r="D596" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E596" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F596" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G596" t="inlineStr">
@@ -26420,22 +26420,22 @@
       </c>
       <c r="C597" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D597" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E597" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F597" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G597" t="inlineStr">
@@ -26468,17 +26468,17 @@
       </c>
       <c r="D598" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E598" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F598" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G598" t="inlineStr">
@@ -26501,32 +26501,32 @@
       </c>
       <c r="B599" t="inlineStr">
         <is>
-          <t>RealTimePayment</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C599" t="inlineStr">
         <is>
-          <t>Qris</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D599" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E599" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F599" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G599" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H599" t="inlineStr">
@@ -26554,17 +26554,17 @@
       </c>
       <c r="D600" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E600" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F600" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G600" t="inlineStr">
@@ -26582,37 +26582,37 @@
     <row r="601">
       <c r="A601" t="inlineStr">
         <is>
-          <t>zen</t>
+          <t>xendit</t>
         </is>
       </c>
       <c r="B601" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>RealTimePayment</t>
         </is>
       </c>
       <c r="C601" t="inlineStr">
         <is>
-          <t>Multibanco</t>
+          <t>Qris</t>
         </is>
       </c>
       <c r="D601" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E601" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F601" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G601" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H601" t="inlineStr">
@@ -26635,7 +26635,7 @@
       </c>
       <c r="C602" t="inlineStr">
         <is>
-          <t>Pix</t>
+          <t>Multibanco</t>
         </is>
       </c>
       <c r="D602" t="inlineStr">
@@ -26678,7 +26678,7 @@
       </c>
       <c r="C603" t="inlineStr">
         <is>
-          <t>Pse</t>
+          <t>Pix</t>
         </is>
       </c>
       <c r="D603" t="inlineStr">
@@ -26716,12 +26716,12 @@
       </c>
       <c r="B604" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C604" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>Pse</t>
         </is>
       </c>
       <c r="D604" t="inlineStr">
@@ -26764,7 +26764,7 @@
       </c>
       <c r="C605" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D605" t="inlineStr">
@@ -26802,12 +26802,12 @@
       </c>
       <c r="B606" t="inlineStr">
         <is>
-          <t>Voucher</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C606" t="inlineStr">
         <is>
-          <t>Boleto</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D606" t="inlineStr">
@@ -26850,7 +26850,7 @@
       </c>
       <c r="C607" t="inlineStr">
         <is>
-          <t>Efecty</t>
+          <t>Boleto</t>
         </is>
       </c>
       <c r="D607" t="inlineStr">
@@ -26893,7 +26893,7 @@
       </c>
       <c r="C608" t="inlineStr">
         <is>
-          <t>PagoEfectivo</t>
+          <t>Efecty</t>
         </is>
       </c>
       <c r="D608" t="inlineStr">
@@ -26936,7 +26936,7 @@
       </c>
       <c r="C609" t="inlineStr">
         <is>
-          <t>RedCompra</t>
+          <t>PagoEfectivo</t>
         </is>
       </c>
       <c r="D609" t="inlineStr">
@@ -26979,7 +26979,7 @@
       </c>
       <c r="C610" t="inlineStr">
         <is>
-          <t>RedPagos</t>
+          <t>RedCompra</t>
         </is>
       </c>
       <c r="D610" t="inlineStr">
@@ -27017,12 +27017,12 @@
       </c>
       <c r="B611" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>Voucher</t>
         </is>
       </c>
       <c r="C611" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>RedPagos</t>
         </is>
       </c>
       <c r="D611" t="inlineStr">
@@ -27065,7 +27065,7 @@
       </c>
       <c r="C612" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D612" t="inlineStr">
@@ -27098,17 +27098,17 @@
     <row r="613">
       <c r="A613" t="inlineStr">
         <is>
-          <t>zift</t>
+          <t>zen</t>
         </is>
       </c>
       <c r="B613" t="inlineStr">
         <is>
-          <t>Card</t>
+          <t>Wallet</t>
         </is>
       </c>
       <c r="C613" t="inlineStr">
         <is>
-          <t>Credit</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D613" t="inlineStr">
@@ -27128,19 +27128,15 @@
       </c>
       <c r="G613" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H613" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I613" t="inlineStr">
-        <is>
-          <t>2026-04-20 02:16:52</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I613" t="inlineStr"/>
     </row>
     <row r="614">
       <c r="A614" t="inlineStr">
@@ -27160,17 +27156,17 @@
       </c>
       <c r="D614" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E614" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F614" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G614" t="inlineStr">
@@ -27180,10 +27176,14 @@
       </c>
       <c r="H614" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I614" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I614" t="inlineStr">
+        <is>
+          <t>2026-04-20 02:16:52</t>
+        </is>
+      </c>
     </row>
     <row r="615">
       <c r="A615" t="inlineStr">
@@ -27198,22 +27198,22 @@
       </c>
       <c r="C615" t="inlineStr">
         <is>
-          <t>Debit</t>
+          <t>Credit</t>
         </is>
       </c>
       <c r="D615" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E615" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F615" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G615" t="inlineStr">
@@ -27223,14 +27223,10 @@
       </c>
       <c r="H615" t="inlineStr">
         <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="I615" t="inlineStr">
-        <is>
-          <t>2026-04-20 20:57:09</t>
-        </is>
-      </c>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="I615" t="inlineStr"/>
     </row>
     <row r="616">
       <c r="A616" t="inlineStr">
@@ -27250,17 +27246,17 @@
       </c>
       <c r="D616" t="inlineStr">
         <is>
-          <t>Mandate</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E616" t="inlineStr">
         <is>
-          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F616" t="inlineStr">
         <is>
-          <t>POST /payments (setup_future_usage+mandate_data)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G616" t="inlineStr">
@@ -27270,45 +27266,49 @@
       </c>
       <c r="H616" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="I616" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="I616" t="inlineStr">
+        <is>
+          <t>2026-04-20 20:57:09</t>
+        </is>
+      </c>
     </row>
     <row r="617">
       <c r="A617" t="inlineStr">
         <is>
-          <t>zsl</t>
+          <t>zift</t>
         </is>
       </c>
       <c r="B617" t="inlineStr">
         <is>
-          <t>BankTransfer</t>
+          <t>Card</t>
         </is>
       </c>
       <c r="C617" t="inlineStr">
         <is>
-          <t>LocalBankTransfer</t>
+          <t>Debit</t>
         </is>
       </c>
       <c r="D617" t="inlineStr">
         <is>
-          <t>Payment</t>
+          <t>Mandate</t>
         </is>
       </c>
       <c r="E617" t="inlineStr">
         <is>
-          <t>Base payment authorization for this connector + PM + PMT combination</t>
+          <t>Recurring/stored credential mandate setup for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F617" t="inlineStr">
         <is>
-          <t>POST /payments</t>
+          <t>POST /payments (setup_future_usage+mandate_data)</t>
         </is>
       </c>
       <c r="G617" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H617" t="inlineStr">
@@ -27321,42 +27321,42 @@
     <row r="618">
       <c r="A618" t="inlineStr">
         <is>
-          <t>adyen</t>
+          <t>zsl</t>
         </is>
       </c>
       <c r="B618" t="inlineStr">
         <is>
-          <t>Wallet</t>
+          <t>BankTransfer</t>
         </is>
       </c>
       <c r="C618" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>LocalBankTransfer</t>
         </is>
       </c>
       <c r="D618" t="inlineStr">
         <is>
-          <t>Payment (Decrypt Flow)</t>
+          <t>Payment</t>
         </is>
       </c>
       <c r="E618" t="inlineStr">
         <is>
-          <t>HS pre-decrypts the wallet token and sends plaintext card data to the connector instead of the encrypted blob</t>
+          <t>Base payment authorization for this connector + PM + PMT combination</t>
         </is>
       </c>
       <c r="F618" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments</t>
         </is>
       </c>
       <c r="G618" t="inlineStr">
         <is>
-          <t>covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H618" t="inlineStr">
         <is>
-          <t>unknown</t>
+          <t>no</t>
         </is>
       </c>
       <c r="I618" t="inlineStr"/>
@@ -27374,7 +27374,7 @@
       </c>
       <c r="C619" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D619" t="inlineStr">
@@ -27389,7 +27389,7 @@
       </c>
       <c r="F619" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G619" t="inlineStr">
@@ -27417,7 +27417,7 @@
       </c>
       <c r="C620" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D620" t="inlineStr">
@@ -27432,7 +27432,7 @@
       </c>
       <c r="F620" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G620" t="inlineStr">
@@ -27450,7 +27450,7 @@
     <row r="621">
       <c r="A621" t="inlineStr">
         <is>
-          <t>archipel</t>
+          <t>adyen</t>
         </is>
       </c>
       <c r="B621" t="inlineStr">
@@ -27460,7 +27460,7 @@
       </c>
       <c r="C621" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D621" t="inlineStr">
@@ -27475,12 +27475,12 @@
       </c>
       <c r="F621" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G621" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>covered</t>
         </is>
       </c>
       <c r="H621" t="inlineStr">
@@ -27493,7 +27493,7 @@
     <row r="622">
       <c r="A622" t="inlineStr">
         <is>
-          <t>bankofamerica</t>
+          <t>archipel</t>
         </is>
       </c>
       <c r="B622" t="inlineStr">
@@ -27546,7 +27546,7 @@
       </c>
       <c r="C623" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D623" t="inlineStr">
@@ -27561,7 +27561,7 @@
       </c>
       <c r="F623" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G623" t="inlineStr">
@@ -27589,7 +27589,7 @@
       </c>
       <c r="C624" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D624" t="inlineStr">
@@ -27604,7 +27604,7 @@
       </c>
       <c r="F624" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G624" t="inlineStr">
@@ -27622,7 +27622,7 @@
     <row r="625">
       <c r="A625" t="inlineStr">
         <is>
-          <t>barclaycard</t>
+          <t>bankofamerica</t>
         </is>
       </c>
       <c r="B625" t="inlineStr">
@@ -27632,7 +27632,7 @@
       </c>
       <c r="C625" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D625" t="inlineStr">
@@ -27647,7 +27647,7 @@
       </c>
       <c r="F625" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G625" t="inlineStr">
@@ -27675,7 +27675,7 @@
       </c>
       <c r="C626" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D626" t="inlineStr">
@@ -27690,7 +27690,7 @@
       </c>
       <c r="F626" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G626" t="inlineStr">
@@ -27718,7 +27718,7 @@
       </c>
       <c r="C627" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D627" t="inlineStr">
@@ -27733,7 +27733,7 @@
       </c>
       <c r="F627" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G627" t="inlineStr">
@@ -27751,7 +27751,7 @@
     <row r="628">
       <c r="A628" t="inlineStr">
         <is>
-          <t>braintree</t>
+          <t>barclaycard</t>
         </is>
       </c>
       <c r="B628" t="inlineStr">
@@ -27761,7 +27761,7 @@
       </c>
       <c r="C628" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D628" t="inlineStr">
@@ -27776,7 +27776,7 @@
       </c>
       <c r="F628" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G628" t="inlineStr">
@@ -27804,7 +27804,7 @@
       </c>
       <c r="C629" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D629" t="inlineStr">
@@ -27819,7 +27819,7 @@
       </c>
       <c r="F629" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G629" t="inlineStr">
@@ -27847,7 +27847,7 @@
       </c>
       <c r="C630" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D630" t="inlineStr">
@@ -27862,7 +27862,7 @@
       </c>
       <c r="F630" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G630" t="inlineStr">
@@ -27880,7 +27880,7 @@
     <row r="631">
       <c r="A631" t="inlineStr">
         <is>
-          <t>checkout</t>
+          <t>braintree</t>
         </is>
       </c>
       <c r="B631" t="inlineStr">
@@ -27890,7 +27890,7 @@
       </c>
       <c r="C631" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D631" t="inlineStr">
@@ -27905,7 +27905,7 @@
       </c>
       <c r="F631" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G631" t="inlineStr">
@@ -27933,7 +27933,7 @@
       </c>
       <c r="C632" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D632" t="inlineStr">
@@ -27948,7 +27948,7 @@
       </c>
       <c r="F632" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G632" t="inlineStr">
@@ -27976,7 +27976,7 @@
       </c>
       <c r="C633" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D633" t="inlineStr">
@@ -27991,7 +27991,7 @@
       </c>
       <c r="F633" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G633" t="inlineStr">
@@ -28009,7 +28009,7 @@
     <row r="634">
       <c r="A634" t="inlineStr">
         <is>
-          <t>cybersource</t>
+          <t>checkout</t>
         </is>
       </c>
       <c r="B634" t="inlineStr">
@@ -28019,7 +28019,7 @@
       </c>
       <c r="C634" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D634" t="inlineStr">
@@ -28034,7 +28034,7 @@
       </c>
       <c r="F634" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G634" t="inlineStr">
@@ -28062,7 +28062,7 @@
       </c>
       <c r="C635" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D635" t="inlineStr">
@@ -28077,7 +28077,7 @@
       </c>
       <c r="F635" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G635" t="inlineStr">
@@ -28105,7 +28105,7 @@
       </c>
       <c r="C636" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D636" t="inlineStr">
@@ -28120,7 +28120,7 @@
       </c>
       <c r="F636" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G636" t="inlineStr">
@@ -28138,7 +28138,7 @@
     <row r="637">
       <c r="A637" t="inlineStr">
         <is>
-          <t>finix</t>
+          <t>cybersource</t>
         </is>
       </c>
       <c r="B637" t="inlineStr">
@@ -28148,7 +28148,7 @@
       </c>
       <c r="C637" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D637" t="inlineStr">
@@ -28163,7 +28163,7 @@
       </c>
       <c r="F637" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G637" t="inlineStr">
@@ -28191,7 +28191,7 @@
       </c>
       <c r="C638" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D638" t="inlineStr">
@@ -28206,7 +28206,7 @@
       </c>
       <c r="F638" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G638" t="inlineStr">
@@ -28234,7 +28234,7 @@
       </c>
       <c r="C639" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D639" t="inlineStr">
@@ -28249,7 +28249,7 @@
       </c>
       <c r="F639" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G639" t="inlineStr">
@@ -28267,7 +28267,7 @@
     <row r="640">
       <c r="A640" t="inlineStr">
         <is>
-          <t>fiserv</t>
+          <t>finix</t>
         </is>
       </c>
       <c r="B640" t="inlineStr">
@@ -28277,7 +28277,7 @@
       </c>
       <c r="C640" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D640" t="inlineStr">
@@ -28292,7 +28292,7 @@
       </c>
       <c r="F640" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G640" t="inlineStr">
@@ -28310,7 +28310,7 @@
     <row r="641">
       <c r="A641" t="inlineStr">
         <is>
-          <t>fiuu</t>
+          <t>fiserv</t>
         </is>
       </c>
       <c r="B641" t="inlineStr">
@@ -28363,7 +28363,7 @@
       </c>
       <c r="C642" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D642" t="inlineStr">
@@ -28378,7 +28378,7 @@
       </c>
       <c r="F642" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G642" t="inlineStr">
@@ -28406,7 +28406,7 @@
       </c>
       <c r="C643" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D643" t="inlineStr">
@@ -28421,7 +28421,7 @@
       </c>
       <c r="F643" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G643" t="inlineStr">
@@ -28439,7 +28439,7 @@
     <row r="644">
       <c r="A644" t="inlineStr">
         <is>
-          <t>gocardless</t>
+          <t>fiuu</t>
         </is>
       </c>
       <c r="B644" t="inlineStr">
@@ -28449,7 +28449,7 @@
       </c>
       <c r="C644" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D644" t="inlineStr">
@@ -28464,12 +28464,12 @@
       </c>
       <c r="F644" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G644" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H644" t="inlineStr">
@@ -28492,7 +28492,7 @@
       </c>
       <c r="C645" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D645" t="inlineStr">
@@ -28507,7 +28507,7 @@
       </c>
       <c r="F645" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G645" t="inlineStr">
@@ -28535,7 +28535,7 @@
       </c>
       <c r="C646" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D646" t="inlineStr">
@@ -28550,7 +28550,7 @@
       </c>
       <c r="F646" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G646" t="inlineStr">
@@ -28568,7 +28568,7 @@
     <row r="647">
       <c r="A647" t="inlineStr">
         <is>
-          <t>hipay</t>
+          <t>gocardless</t>
         </is>
       </c>
       <c r="B647" t="inlineStr">
@@ -28578,7 +28578,7 @@
       </c>
       <c r="C647" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D647" t="inlineStr">
@@ -28593,12 +28593,12 @@
       </c>
       <c r="F647" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G647" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H647" t="inlineStr">
@@ -28621,7 +28621,7 @@
       </c>
       <c r="C648" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D648" t="inlineStr">
@@ -28636,7 +28636,7 @@
       </c>
       <c r="F648" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G648" t="inlineStr">
@@ -28664,7 +28664,7 @@
       </c>
       <c r="C649" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D649" t="inlineStr">
@@ -28679,7 +28679,7 @@
       </c>
       <c r="F649" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G649" t="inlineStr">
@@ -28697,7 +28697,7 @@
     <row r="650">
       <c r="A650" t="inlineStr">
         <is>
-          <t>mollie</t>
+          <t>hipay</t>
         </is>
       </c>
       <c r="B650" t="inlineStr">
@@ -28707,7 +28707,7 @@
       </c>
       <c r="C650" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D650" t="inlineStr">
@@ -28722,7 +28722,7 @@
       </c>
       <c r="F650" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G650" t="inlineStr">
@@ -28750,7 +28750,7 @@
       </c>
       <c r="C651" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D651" t="inlineStr">
@@ -28765,7 +28765,7 @@
       </c>
       <c r="F651" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G651" t="inlineStr">
@@ -28793,7 +28793,7 @@
       </c>
       <c r="C652" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D652" t="inlineStr">
@@ -28808,7 +28808,7 @@
       </c>
       <c r="F652" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G652" t="inlineStr">
@@ -28826,7 +28826,7 @@
     <row r="653">
       <c r="A653" t="inlineStr">
         <is>
-          <t>nmi</t>
+          <t>mollie</t>
         </is>
       </c>
       <c r="B653" t="inlineStr">
@@ -28836,7 +28836,7 @@
       </c>
       <c r="C653" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D653" t="inlineStr">
@@ -28851,7 +28851,7 @@
       </c>
       <c r="F653" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G653" t="inlineStr">
@@ -28879,7 +28879,7 @@
       </c>
       <c r="C654" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D654" t="inlineStr">
@@ -28894,7 +28894,7 @@
       </c>
       <c r="F654" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G654" t="inlineStr">
@@ -28922,7 +28922,7 @@
       </c>
       <c r="C655" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D655" t="inlineStr">
@@ -28937,7 +28937,7 @@
       </c>
       <c r="F655" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G655" t="inlineStr">
@@ -28955,7 +28955,7 @@
     <row r="656">
       <c r="A656" t="inlineStr">
         <is>
-          <t>nuvei</t>
+          <t>nmi</t>
         </is>
       </c>
       <c r="B656" t="inlineStr">
@@ -28965,7 +28965,7 @@
       </c>
       <c r="C656" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D656" t="inlineStr">
@@ -28980,7 +28980,7 @@
       </c>
       <c r="F656" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G656" t="inlineStr">
@@ -29008,7 +29008,7 @@
       </c>
       <c r="C657" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D657" t="inlineStr">
@@ -29023,7 +29023,7 @@
       </c>
       <c r="F657" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G657" t="inlineStr">
@@ -29041,7 +29041,7 @@
     <row r="658">
       <c r="A658" t="inlineStr">
         <is>
-          <t>payme</t>
+          <t>nuvei</t>
         </is>
       </c>
       <c r="B658" t="inlineStr">
@@ -29051,7 +29051,7 @@
       </c>
       <c r="C658" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D658" t="inlineStr">
@@ -29066,12 +29066,12 @@
       </c>
       <c r="F658" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G658" t="inlineStr">
         <is>
-          <t>no_cypress_config</t>
+          <t>not_covered</t>
         </is>
       </c>
       <c r="H658" t="inlineStr">
@@ -29094,7 +29094,7 @@
       </c>
       <c r="C659" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D659" t="inlineStr">
@@ -29109,7 +29109,7 @@
       </c>
       <c r="F659" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G659" t="inlineStr">
@@ -29137,7 +29137,7 @@
       </c>
       <c r="C660" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D660" t="inlineStr">
@@ -29152,7 +29152,7 @@
       </c>
       <c r="F660" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G660" t="inlineStr">
@@ -29170,7 +29170,7 @@
     <row r="661">
       <c r="A661" t="inlineStr">
         <is>
-          <t>paysafe</t>
+          <t>payme</t>
         </is>
       </c>
       <c r="B661" t="inlineStr">
@@ -29180,7 +29180,7 @@
       </c>
       <c r="C661" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D661" t="inlineStr">
@@ -29195,12 +29195,12 @@
       </c>
       <c r="F661" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G661" t="inlineStr">
         <is>
-          <t>not_covered</t>
+          <t>no_cypress_config</t>
         </is>
       </c>
       <c r="H661" t="inlineStr">
@@ -29213,7 +29213,7 @@
     <row r="662">
       <c r="A662" t="inlineStr">
         <is>
-          <t>square</t>
+          <t>paysafe</t>
         </is>
       </c>
       <c r="B662" t="inlineStr">
@@ -29266,7 +29266,7 @@
       </c>
       <c r="C663" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D663" t="inlineStr">
@@ -29281,7 +29281,7 @@
       </c>
       <c r="F663" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G663" t="inlineStr">
@@ -29309,7 +29309,7 @@
       </c>
       <c r="C664" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D664" t="inlineStr">
@@ -29324,7 +29324,7 @@
       </c>
       <c r="F664" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G664" t="inlineStr">
@@ -29342,7 +29342,7 @@
     <row r="665">
       <c r="A665" t="inlineStr">
         <is>
-          <t>stax</t>
+          <t>square</t>
         </is>
       </c>
       <c r="B665" t="inlineStr">
@@ -29352,7 +29352,7 @@
       </c>
       <c r="C665" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D665" t="inlineStr">
@@ -29367,7 +29367,7 @@
       </c>
       <c r="F665" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G665" t="inlineStr">
@@ -29395,7 +29395,7 @@
       </c>
       <c r="C666" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D666" t="inlineStr">
@@ -29410,7 +29410,7 @@
       </c>
       <c r="F666" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G666" t="inlineStr">
@@ -29438,7 +29438,7 @@
       </c>
       <c r="C667" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D667" t="inlineStr">
@@ -29453,7 +29453,7 @@
       </c>
       <c r="F667" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G667" t="inlineStr">
@@ -29471,7 +29471,7 @@
     <row r="668">
       <c r="A668" t="inlineStr">
         <is>
-          <t>stripe</t>
+          <t>stax</t>
         </is>
       </c>
       <c r="B668" t="inlineStr">
@@ -29481,7 +29481,7 @@
       </c>
       <c r="C668" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D668" t="inlineStr">
@@ -29496,7 +29496,7 @@
       </c>
       <c r="F668" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G668" t="inlineStr">
@@ -29524,7 +29524,7 @@
       </c>
       <c r="C669" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D669" t="inlineStr">
@@ -29539,7 +29539,7 @@
       </c>
       <c r="F669" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G669" t="inlineStr">
@@ -29567,7 +29567,7 @@
       </c>
       <c r="C670" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D670" t="inlineStr">
@@ -29582,7 +29582,7 @@
       </c>
       <c r="F670" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G670" t="inlineStr">
@@ -29600,7 +29600,7 @@
     <row r="671">
       <c r="A671" t="inlineStr">
         <is>
-          <t>tesouro</t>
+          <t>stripe</t>
         </is>
       </c>
       <c r="B671" t="inlineStr">
@@ -29610,7 +29610,7 @@
       </c>
       <c r="C671" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D671" t="inlineStr">
@@ -29625,7 +29625,7 @@
       </c>
       <c r="F671" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G671" t="inlineStr">
@@ -29653,7 +29653,7 @@
       </c>
       <c r="C672" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D672" t="inlineStr">
@@ -29668,7 +29668,7 @@
       </c>
       <c r="F672" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G672" t="inlineStr">
@@ -29686,7 +29686,7 @@
     <row r="673">
       <c r="A673" t="inlineStr">
         <is>
-          <t>wellsfargo</t>
+          <t>tesouro</t>
         </is>
       </c>
       <c r="B673" t="inlineStr">
@@ -29696,7 +29696,7 @@
       </c>
       <c r="C673" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D673" t="inlineStr">
@@ -29711,7 +29711,7 @@
       </c>
       <c r="F673" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G673" t="inlineStr">
@@ -29739,7 +29739,7 @@
       </c>
       <c r="C674" t="inlineStr">
         <is>
-          <t>GooglePay</t>
+          <t>ApplePay</t>
         </is>
       </c>
       <c r="D674" t="inlineStr">
@@ -29754,7 +29754,7 @@
       </c>
       <c r="F674" t="inlineStr">
         <is>
-          <t>POST /payments (GooglePay pre-decrypted token)</t>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G674" t="inlineStr">
@@ -29782,7 +29782,7 @@
       </c>
       <c r="C675" t="inlineStr">
         <is>
-          <t>Paze</t>
+          <t>GooglePay</t>
         </is>
       </c>
       <c r="D675" t="inlineStr">
@@ -29797,7 +29797,7 @@
       </c>
       <c r="F675" t="inlineStr">
         <is>
-          <t>POST /payments (Paze pre-decrypted token)</t>
+          <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
       <c r="G675" t="inlineStr">
@@ -29815,7 +29815,7 @@
     <row r="676">
       <c r="A676" t="inlineStr">
         <is>
-          <t>worldpayvantiv</t>
+          <t>wellsfargo</t>
         </is>
       </c>
       <c r="B676" t="inlineStr">
@@ -29825,7 +29825,7 @@
       </c>
       <c r="C676" t="inlineStr">
         <is>
-          <t>ApplePay</t>
+          <t>Paze</t>
         </is>
       </c>
       <c r="D676" t="inlineStr">
@@ -29840,7 +29840,7 @@
       </c>
       <c r="F676" t="inlineStr">
         <is>
-          <t>POST /payments (ApplePay pre-decrypted token)</t>
+          <t>POST /payments (Paze pre-decrypted token)</t>
         </is>
       </c>
       <c r="G676" t="inlineStr">
@@ -29868,35 +29868,78 @@
       </c>
       <c r="C677" t="inlineStr">
         <is>
+          <t>ApplePay</t>
+        </is>
+      </c>
+      <c r="D677" t="inlineStr">
+        <is>
+          <t>Payment (Decrypt Flow)</t>
+        </is>
+      </c>
+      <c r="E677" t="inlineStr">
+        <is>
+          <t>HS pre-decrypts the wallet token and sends plaintext card data to the connector instead of the encrypted blob</t>
+        </is>
+      </c>
+      <c r="F677" t="inlineStr">
+        <is>
+          <t>POST /payments (ApplePay pre-decrypted token)</t>
+        </is>
+      </c>
+      <c r="G677" t="inlineStr">
+        <is>
+          <t>not_covered</t>
+        </is>
+      </c>
+      <c r="H677" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="I677" t="inlineStr"/>
+    </row>
+    <row r="678">
+      <c r="A678" t="inlineStr">
+        <is>
+          <t>worldpayvantiv</t>
+        </is>
+      </c>
+      <c r="B678" t="inlineStr">
+        <is>
+          <t>Wallet</t>
+        </is>
+      </c>
+      <c r="C678" t="inlineStr">
+        <is>
           <t>GooglePay</t>
         </is>
       </c>
-      <c r="D677" t="inlineStr">
+      <c r="D678" t="inlineStr">
         <is>
           <t>Payment (Decrypt Flow)</t>
         </is>
       </c>
-      <c r="E677" t="inlineStr">
+      <c r="E678" t="inlineStr">
         <is>
           <t>HS pre-decrypts the wallet token and sends plaintext card data to the connector instead of the encrypted blob</t>
         </is>
       </c>
-      <c r="F677" t="inlineStr">
+      <c r="F678" t="inlineStr">
         <is>
           <t>POST /payments (GooglePay pre-decrypted token)</t>
         </is>
       </c>
-      <c r="G677" t="inlineStr">
+      <c r="G678" t="inlineStr">
         <is>
           <t>not_covered</t>
         </is>
       </c>
-      <c r="H677" t="inlineStr">
+      <c r="H678" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="I677" t="inlineStr"/>
+      <c r="I678" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
